--- a/Data/EXCEL/Transfer/salemon/202208/4147-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/4147-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BEAA5DF-9740-436D-930E-C1F46FB28E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF3E7389-40CE-49A6-82CB-E4015183223D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="4147-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -261,9 +261,9 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -845,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1218,19 +1226,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q151"/>
+  <dimension ref="A1:Q152"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="8.5" customWidth="1"/>
-    <col min="7" max="7" width="9.875" customWidth="1"/>
-    <col min="8" max="8" width="10.25" customWidth="1"/>
-    <col min="9" max="9" width="11.625" customWidth="1"/>
-    <col min="10" max="13" width="10.25" customWidth="1"/>
-    <col min="14" max="14" width="11.625" customWidth="1"/>
-    <col min="15" max="16" width="10.25" customWidth="1"/>
-    <col min="17" max="17" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="2" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="12.125" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14.625" customWidth="1"/>
+    <col min="9" max="9" width="16.5" customWidth="1"/>
+    <col min="10" max="13" width="14.625" customWidth="1"/>
+    <col min="14" max="14" width="16.5" customWidth="1"/>
+    <col min="15" max="16" width="14.625" customWidth="1"/>
+    <col min="17" max="17" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1383,2225 +1391,2225 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44743</v>
+        <v>44774</v>
       </c>
       <c r="B5" s="7">
-        <v>62</v>
+        <v>57.2</v>
       </c>
       <c r="C5" s="7">
-        <v>57.3</v>
+        <v>72.8</v>
       </c>
       <c r="D5" s="7">
-        <v>62</v>
+        <v>72.8</v>
       </c>
       <c r="E5" s="7">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-4.7</v>
+        <v>15.5</v>
       </c>
       <c r="G5" s="8">
-        <v>-7.58</v>
+        <v>27.05</v>
       </c>
       <c r="H5" s="9">
-        <v>0.28100000000000003</v>
-      </c>
-      <c r="I5" s="10">
-        <v>2.52</v>
-      </c>
-      <c r="J5" s="8">
-        <v>-12.8</v>
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="I5" s="8">
+        <v>6.52</v>
+      </c>
+      <c r="J5" s="10">
+        <v>-3.04</v>
       </c>
       <c r="K5" s="9">
-        <v>1.68</v>
-      </c>
-      <c r="L5" s="8">
-        <v>-39.700000000000003</v>
+        <v>1.98</v>
+      </c>
+      <c r="L5" s="10">
+        <v>-36</v>
       </c>
       <c r="M5" s="9">
-        <v>0.28100000000000003</v>
-      </c>
-      <c r="N5" s="10">
-        <v>2.52</v>
-      </c>
-      <c r="O5" s="8">
-        <v>-12.8</v>
+        <v>0.29899999999999999</v>
+      </c>
+      <c r="N5" s="8">
+        <v>6.52</v>
+      </c>
+      <c r="O5" s="10">
+        <v>-3.04</v>
       </c>
       <c r="P5" s="9">
-        <v>1.68</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>-39.700000000000003</v>
+        <v>1.98</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>-36</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44713</v>
+        <v>44743</v>
       </c>
       <c r="B6" s="7">
-        <v>63.6</v>
+        <v>62</v>
       </c>
       <c r="C6" s="7">
+        <v>57.3</v>
+      </c>
+      <c r="D6" s="7">
         <v>62</v>
       </c>
-      <c r="D6" s="7">
-        <v>65.8</v>
-      </c>
       <c r="E6" s="7">
-        <v>59.8</v>
-      </c>
-      <c r="F6" s="8">
-        <v>-1.6</v>
-      </c>
-      <c r="G6" s="8">
-        <v>-2.52</v>
+        <v>52.2</v>
+      </c>
+      <c r="F6" s="10">
+        <v>-4.7</v>
+      </c>
+      <c r="G6" s="10">
+        <v>-7.58</v>
       </c>
       <c r="H6" s="9">
-        <v>0.27400000000000002</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="I6" s="8">
-        <v>-12.5</v>
-      </c>
-      <c r="J6" s="8">
-        <v>-41.1</v>
+        <v>2.52</v>
+      </c>
+      <c r="J6" s="10">
+        <v>-12.8</v>
       </c>
       <c r="K6" s="9">
-        <v>1.4</v>
-      </c>
-      <c r="L6" s="8">
-        <v>-43.2</v>
+        <v>1.68</v>
+      </c>
+      <c r="L6" s="10">
+        <v>-39.700000000000003</v>
       </c>
       <c r="M6" s="9">
-        <v>0.27400000000000002</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="N6" s="8">
-        <v>-12.5</v>
-      </c>
-      <c r="O6" s="8">
-        <v>-41.1</v>
+        <v>2.52</v>
+      </c>
+      <c r="O6" s="10">
+        <v>-12.8</v>
       </c>
       <c r="P6" s="9">
-        <v>1.4</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>-43.2</v>
+        <v>1.68</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>-39.700000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B7" s="7">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
       <c r="C7" s="7">
-        <v>63.6</v>
+        <v>62</v>
       </c>
       <c r="D7" s="7">
-        <v>67</v>
+        <v>65.8</v>
       </c>
       <c r="E7" s="7">
-        <v>58.7</v>
+        <v>59.8</v>
       </c>
       <c r="F7" s="10">
-        <v>1</v>
+        <v>-1.6</v>
       </c>
       <c r="G7" s="10">
-        <v>1.6</v>
+        <v>-2.52</v>
       </c>
       <c r="H7" s="9">
-        <v>0.313</v>
-      </c>
-      <c r="I7" s="8">
-        <v>-22.8</v>
-      </c>
-      <c r="J7" s="8">
-        <v>-39.6</v>
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="I7" s="10">
+        <v>-12.5</v>
+      </c>
+      <c r="J7" s="10">
+        <v>-41.1</v>
       </c>
       <c r="K7" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="L7" s="8">
-        <v>-43.7</v>
+        <v>1.4</v>
+      </c>
+      <c r="L7" s="10">
+        <v>-43.2</v>
       </c>
       <c r="M7" s="9">
-        <v>0.313</v>
-      </c>
-      <c r="N7" s="8">
-        <v>-22.8</v>
-      </c>
-      <c r="O7" s="8">
-        <v>-39.6</v>
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="N7" s="10">
+        <v>-12.5</v>
+      </c>
+      <c r="O7" s="10">
+        <v>-41.1</v>
       </c>
       <c r="P7" s="9">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>-43.7</v>
+        <v>1.4</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>-43.2</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B8" s="7">
-        <v>63.1</v>
+        <v>62.5</v>
       </c>
       <c r="C8" s="7">
-        <v>62.6</v>
+        <v>63.6</v>
       </c>
       <c r="D8" s="7">
-        <v>71.8</v>
+        <v>67</v>
       </c>
       <c r="E8" s="7">
-        <v>61.2</v>
+        <v>58.7</v>
       </c>
       <c r="F8" s="8">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="8">
-        <v>-0.79</v>
+        <v>1.6</v>
       </c>
       <c r="H8" s="9">
-        <v>0.40600000000000003</v>
+        <v>0.313</v>
       </c>
       <c r="I8" s="10">
-        <v>214.9</v>
-      </c>
-      <c r="J8" s="8">
-        <v>-28.7</v>
+        <v>-22.8</v>
+      </c>
+      <c r="J8" s="10">
+        <v>-39.6</v>
       </c>
       <c r="K8" s="9">
-        <v>0.81200000000000006</v>
-      </c>
-      <c r="L8" s="8">
-        <v>-45.2</v>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="L8" s="10">
+        <v>-43.7</v>
       </c>
       <c r="M8" s="9">
-        <v>0.40600000000000003</v>
+        <v>0.313</v>
       </c>
       <c r="N8" s="10">
-        <v>214.9</v>
-      </c>
-      <c r="O8" s="8">
-        <v>-28.7</v>
+        <v>-22.8</v>
+      </c>
+      <c r="O8" s="10">
+        <v>-39.6</v>
       </c>
       <c r="P8" s="9">
-        <v>0.81200000000000006</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>-45.2</v>
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>-43.7</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B9" s="7">
-        <v>69.7</v>
+        <v>63.1</v>
       </c>
       <c r="C9" s="7">
-        <v>63.1</v>
+        <v>62.6</v>
       </c>
       <c r="D9" s="7">
-        <v>69.7</v>
+        <v>71.8</v>
       </c>
       <c r="E9" s="7">
-        <v>60.9</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-6</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-8.68</v>
+        <v>61.2</v>
+      </c>
+      <c r="F9" s="10">
+        <v>-0.5</v>
+      </c>
+      <c r="G9" s="10">
+        <v>-0.79</v>
       </c>
       <c r="H9" s="9">
-        <v>0.129</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="I9" s="8">
-        <v>-10.199999999999999</v>
+        <v>214.9</v>
       </c>
       <c r="J9" s="10">
-        <v>46.7</v>
+        <v>-28.7</v>
       </c>
       <c r="K9" s="9">
-        <v>0.40699999999999997</v>
-      </c>
-      <c r="L9" s="8">
-        <v>-55.4</v>
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="L9" s="10">
+        <v>-45.2</v>
       </c>
       <c r="M9" s="9">
-        <v>0.129</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="N9" s="8">
-        <v>-10.199999999999999</v>
+        <v>214.9</v>
       </c>
       <c r="O9" s="10">
-        <v>46.7</v>
+        <v>-28.7</v>
       </c>
       <c r="P9" s="9">
-        <v>0.40699999999999997</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>-55.4</v>
+        <v>0.81200000000000006</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>-45.2</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B10" s="7">
-        <v>68.2</v>
+        <v>69.7</v>
       </c>
       <c r="C10" s="7">
-        <v>69.099999999999994</v>
+        <v>63.1</v>
       </c>
       <c r="D10" s="7">
-        <v>73.400000000000006</v>
+        <v>69.7</v>
       </c>
       <c r="E10" s="7">
-        <v>68.099999999999994</v>
+        <v>60.9</v>
       </c>
       <c r="F10" s="10">
-        <v>2.2000000000000002</v>
+        <v>-6</v>
       </c>
       <c r="G10" s="10">
-        <v>3.29</v>
+        <v>-8.68</v>
       </c>
       <c r="H10" s="9">
-        <v>0.14399999999999999</v>
+        <v>0.129</v>
       </c>
       <c r="I10" s="10">
-        <v>6.95</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="J10" s="8">
-        <v>-65.099999999999994</v>
+        <v>46.7</v>
       </c>
       <c r="K10" s="9">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="L10" s="8">
-        <v>-66.3</v>
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="L10" s="10">
+        <v>-55.4</v>
       </c>
       <c r="M10" s="9">
-        <v>0.14399999999999999</v>
+        <v>0.129</v>
       </c>
       <c r="N10" s="10">
-        <v>6.95</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="O10" s="8">
-        <v>-65.099999999999994</v>
+        <v>46.7</v>
       </c>
       <c r="P10" s="9">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>-66.3</v>
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>-55.4</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B11" s="7">
-        <v>71.099999999999994</v>
+        <v>68.2</v>
       </c>
       <c r="C11" s="7">
-        <v>66.900000000000006</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="D11" s="7">
-        <v>71.099999999999994</v>
+        <v>73.400000000000006</v>
       </c>
       <c r="E11" s="7">
-        <v>66</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="F11" s="8">
-        <v>-3.7</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G11" s="8">
-        <v>-5.24</v>
+        <v>3.29</v>
       </c>
       <c r="H11" s="9">
-        <v>0.13400000000000001</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="I11" s="8">
-        <v>-27.9</v>
-      </c>
-      <c r="J11" s="8">
-        <v>-67.5</v>
+        <v>6.95</v>
+      </c>
+      <c r="J11" s="10">
+        <v>-65.099999999999994</v>
       </c>
       <c r="K11" s="9">
-        <v>0.13400000000000001</v>
-      </c>
-      <c r="L11" s="8">
-        <v>-67.5</v>
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="L11" s="10">
+        <v>-66.3</v>
       </c>
       <c r="M11" s="9">
-        <v>0.13400000000000001</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="N11" s="8">
-        <v>-27.9</v>
-      </c>
-      <c r="O11" s="8">
-        <v>-67.5</v>
+        <v>6.95</v>
+      </c>
+      <c r="O11" s="10">
+        <v>-65.099999999999994</v>
       </c>
       <c r="P11" s="9">
-        <v>0.13400000000000001</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>-67.5</v>
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>-66.3</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B12" s="7">
-        <v>68.900000000000006</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="C12" s="7">
-        <v>70.599999999999994</v>
+        <v>66.900000000000006</v>
       </c>
       <c r="D12" s="7">
-        <v>77.2</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="E12" s="7">
-        <v>68.599999999999994</v>
+        <v>66</v>
       </c>
       <c r="F12" s="10">
-        <v>1.1000000000000001</v>
+        <v>-3.7</v>
       </c>
       <c r="G12" s="10">
-        <v>1.58</v>
+        <v>-5.24</v>
       </c>
       <c r="H12" s="9">
-        <v>0.186</v>
-      </c>
-      <c r="I12" s="8">
-        <v>-11.7</v>
-      </c>
-      <c r="J12" s="8">
-        <v>-53.8</v>
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="I12" s="10">
+        <v>-27.9</v>
+      </c>
+      <c r="J12" s="10">
+        <v>-67.5</v>
       </c>
       <c r="K12" s="9">
-        <v>4.13</v>
-      </c>
-      <c r="L12" s="8">
-        <v>-42.8</v>
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="L12" s="10">
+        <v>-67.5</v>
       </c>
       <c r="M12" s="9">
-        <v>0.186</v>
-      </c>
-      <c r="N12" s="8">
-        <v>-11.7</v>
-      </c>
-      <c r="O12" s="8">
-        <v>-53.8</v>
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="N12" s="10">
+        <v>-27.9</v>
+      </c>
+      <c r="O12" s="10">
+        <v>-67.5</v>
       </c>
       <c r="P12" s="9">
-        <v>4.13</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>-42.8</v>
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>-67.5</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B13" s="7">
-        <v>67.5</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="C13" s="7">
-        <v>69.5</v>
+        <v>70.599999999999994</v>
       </c>
       <c r="D13" s="7">
-        <v>73.900000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="E13" s="7">
-        <v>65.2</v>
-      </c>
-      <c r="F13" s="10">
-        <v>2.7</v>
-      </c>
-      <c r="G13" s="10">
-        <v>4.04</v>
+        <v>68.599999999999994</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1.58</v>
       </c>
       <c r="H13" s="9">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="I13" s="8">
-        <v>-41.6</v>
-      </c>
-      <c r="J13" s="8">
-        <v>-62.3</v>
+        <v>0.186</v>
+      </c>
+      <c r="I13" s="10">
+        <v>-11.7</v>
+      </c>
+      <c r="J13" s="10">
+        <v>-53.8</v>
       </c>
       <c r="K13" s="9">
-        <v>3.95</v>
-      </c>
-      <c r="L13" s="8">
-        <v>-42.1</v>
+        <v>4.13</v>
+      </c>
+      <c r="L13" s="10">
+        <v>-42.8</v>
       </c>
       <c r="M13" s="9">
-        <v>0.21099999999999999</v>
-      </c>
-      <c r="N13" s="8">
-        <v>-41.6</v>
-      </c>
-      <c r="O13" s="8">
-        <v>-62.3</v>
+        <v>0.186</v>
+      </c>
+      <c r="N13" s="10">
+        <v>-11.7</v>
+      </c>
+      <c r="O13" s="10">
+        <v>-53.8</v>
       </c>
       <c r="P13" s="9">
-        <v>3.95</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>-42.1</v>
+        <v>4.13</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>-42.8</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B14" s="7">
-        <v>83</v>
+        <v>67.5</v>
       </c>
       <c r="C14" s="7">
-        <v>66.8</v>
+        <v>69.5</v>
       </c>
       <c r="D14" s="7">
-        <v>85</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="E14" s="7">
-        <v>65</v>
+        <v>65.2</v>
       </c>
       <c r="F14" s="8">
-        <v>-12.6</v>
+        <v>2.7</v>
       </c>
       <c r="G14" s="8">
-        <v>-15.87</v>
+        <v>4.04</v>
       </c>
       <c r="H14" s="9">
-        <v>0.36099999999999999</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="I14" s="10">
-        <v>28.9</v>
-      </c>
-      <c r="J14" s="8">
-        <v>-36.700000000000003</v>
+        <v>-41.6</v>
+      </c>
+      <c r="J14" s="10">
+        <v>-62.3</v>
       </c>
       <c r="K14" s="9">
-        <v>3.74</v>
-      </c>
-      <c r="L14" s="8">
-        <v>-40.299999999999997</v>
+        <v>3.95</v>
+      </c>
+      <c r="L14" s="10">
+        <v>-42.1</v>
       </c>
       <c r="M14" s="9">
-        <v>0.36099999999999999</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="N14" s="10">
-        <v>28.9</v>
-      </c>
-      <c r="O14" s="8">
-        <v>-36.700000000000003</v>
+        <v>-41.6</v>
+      </c>
+      <c r="O14" s="10">
+        <v>-62.3</v>
       </c>
       <c r="P14" s="9">
-        <v>3.74</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>-40.299999999999997</v>
+        <v>3.95</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>-42.1</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B15" s="7">
-        <v>63.8</v>
+        <v>83</v>
       </c>
       <c r="C15" s="7">
-        <v>79.400000000000006</v>
+        <v>66.8</v>
       </c>
       <c r="D15" s="7">
-        <v>79.400000000000006</v>
+        <v>85</v>
       </c>
       <c r="E15" s="7">
-        <v>61.1</v>
+        <v>65</v>
       </c>
       <c r="F15" s="10">
-        <v>15.9</v>
+        <v>-12.6</v>
       </c>
       <c r="G15" s="10">
-        <v>25.04</v>
+        <v>-15.87</v>
       </c>
       <c r="H15" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="I15" s="8">
-        <v>-9.17</v>
+        <v>28.9</v>
       </c>
       <c r="J15" s="10">
-        <v>6855.8</v>
+        <v>-36.700000000000003</v>
       </c>
       <c r="K15" s="9">
-        <v>3.38</v>
-      </c>
-      <c r="L15" s="8">
-        <v>-40.700000000000003</v>
+        <v>3.74</v>
+      </c>
+      <c r="L15" s="10">
+        <v>-40.299999999999997</v>
       </c>
       <c r="M15" s="9">
-        <v>0.28000000000000003</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="N15" s="8">
-        <v>-9.17</v>
+        <v>28.9</v>
       </c>
       <c r="O15" s="10">
-        <v>6855.8</v>
+        <v>-36.700000000000003</v>
       </c>
       <c r="P15" s="9">
-        <v>3.38</v>
-      </c>
-      <c r="Q15" s="8">
-        <v>-40.700000000000003</v>
+        <v>3.74</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>-40.299999999999997</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B16" s="7">
-        <v>63.1</v>
+        <v>63.8</v>
       </c>
       <c r="C16" s="7">
-        <v>63.5</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="D16" s="7">
-        <v>69.900000000000006</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="E16" s="7">
-        <v>61.5</v>
-      </c>
-      <c r="F16" s="10">
-        <v>0.6</v>
-      </c>
-      <c r="G16" s="10">
-        <v>0.95</v>
+        <v>61.1</v>
+      </c>
+      <c r="F16" s="8">
+        <v>15.9</v>
+      </c>
+      <c r="G16" s="8">
+        <v>25.04</v>
       </c>
       <c r="H16" s="9">
-        <v>0.309</v>
-      </c>
-      <c r="I16" s="8">
-        <v>-4.22</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I16" s="10">
+        <v>-9.17</v>
       </c>
       <c r="J16" s="8">
-        <v>-43.4</v>
+        <v>6855.8</v>
       </c>
       <c r="K16" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="L16" s="8">
-        <v>-45.6</v>
+        <v>3.38</v>
+      </c>
+      <c r="L16" s="10">
+        <v>-40.700000000000003</v>
       </c>
       <c r="M16" s="9">
-        <v>0.309</v>
-      </c>
-      <c r="N16" s="8">
-        <v>-4.22</v>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="N16" s="10">
+        <v>-9.17</v>
       </c>
       <c r="O16" s="8">
-        <v>-43.4</v>
+        <v>6855.8</v>
       </c>
       <c r="P16" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="Q16" s="8">
-        <v>-45.6</v>
+        <v>3.38</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>-40.700000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B17" s="7">
-        <v>66.5</v>
+        <v>63.1</v>
       </c>
       <c r="C17" s="7">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="D17" s="7">
-        <v>68</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="E17" s="7">
-        <v>61</v>
+        <v>61.5</v>
       </c>
       <c r="F17" s="8">
-        <v>-3.4</v>
+        <v>0.6</v>
       </c>
       <c r="G17" s="8">
-        <v>-5.13</v>
+        <v>0.95</v>
       </c>
       <c r="H17" s="9">
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="I17" s="8">
-        <v>-30.7</v>
-      </c>
-      <c r="J17" s="8">
-        <v>-66.400000000000006</v>
+        <v>0.309</v>
+      </c>
+      <c r="I17" s="10">
+        <v>-4.22</v>
+      </c>
+      <c r="J17" s="10">
+        <v>-43.4</v>
       </c>
       <c r="K17" s="9">
-        <v>2.79</v>
-      </c>
-      <c r="L17" s="8">
-        <v>-45.8</v>
+        <v>3.1</v>
+      </c>
+      <c r="L17" s="10">
+        <v>-45.6</v>
       </c>
       <c r="M17" s="9">
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="N17" s="8">
-        <v>-30.7</v>
-      </c>
-      <c r="O17" s="8">
-        <v>-66.400000000000006</v>
+        <v>0.309</v>
+      </c>
+      <c r="N17" s="10">
+        <v>-4.22</v>
+      </c>
+      <c r="O17" s="10">
+        <v>-43.4</v>
       </c>
       <c r="P17" s="9">
-        <v>2.79</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>-45.8</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>-45.6</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B18" s="7">
-        <v>75.400000000000006</v>
+        <v>66.5</v>
       </c>
       <c r="C18" s="7">
-        <v>66.3</v>
+        <v>62.9</v>
       </c>
       <c r="D18" s="7">
-        <v>75.400000000000006</v>
+        <v>68</v>
       </c>
       <c r="E18" s="7">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="F18" s="8">
-        <v>-9.6999999999999993</v>
-      </c>
-      <c r="G18" s="8">
-        <v>-12.76</v>
+        <v>61</v>
+      </c>
+      <c r="F18" s="10">
+        <v>-3.4</v>
+      </c>
+      <c r="G18" s="10">
+        <v>-5.13</v>
       </c>
       <c r="H18" s="9">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="I18" s="8">
-        <v>-10.199999999999999</v>
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="I18" s="10">
+        <v>-30.7</v>
       </c>
       <c r="J18" s="10">
-        <v>0.92</v>
+        <v>-66.400000000000006</v>
       </c>
       <c r="K18" s="9">
-        <v>2.46</v>
-      </c>
-      <c r="L18" s="8">
-        <v>-41.1</v>
+        <v>2.79</v>
+      </c>
+      <c r="L18" s="10">
+        <v>-45.8</v>
       </c>
       <c r="M18" s="9">
-        <v>0.46500000000000002</v>
-      </c>
-      <c r="N18" s="8">
-        <v>-10.199999999999999</v>
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="N18" s="10">
+        <v>-30.7</v>
       </c>
       <c r="O18" s="10">
-        <v>0.92</v>
+        <v>-66.400000000000006</v>
       </c>
       <c r="P18" s="9">
-        <v>2.46</v>
-      </c>
-      <c r="Q18" s="8">
-        <v>-41.1</v>
+        <v>2.79</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>-45.8</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B19" s="7">
-        <v>72.8</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="C19" s="7">
-        <v>76</v>
+        <v>66.3</v>
       </c>
       <c r="D19" s="7">
-        <v>76.2</v>
+        <v>75.400000000000006</v>
       </c>
       <c r="E19" s="7">
-        <v>59.2</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="F19" s="10">
-        <v>3.9</v>
+        <v>-9.6999999999999993</v>
       </c>
       <c r="G19" s="10">
-        <v>5.41</v>
+        <v>-12.76</v>
       </c>
       <c r="H19" s="9">
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="I19" s="8">
-        <v>-8.99</v>
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="I19" s="10">
+        <v>-10.199999999999999</v>
       </c>
       <c r="J19" s="8">
-        <v>-18.899999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="K19" s="9">
-        <v>2</v>
-      </c>
-      <c r="L19" s="8">
-        <v>-46.3</v>
+        <v>2.46</v>
+      </c>
+      <c r="L19" s="10">
+        <v>-41.1</v>
       </c>
       <c r="M19" s="9">
-        <v>0.51800000000000002</v>
-      </c>
-      <c r="N19" s="8">
-        <v>-8.99</v>
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="N19" s="10">
+        <v>-10.199999999999999</v>
       </c>
       <c r="O19" s="8">
-        <v>-18.899999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="P19" s="9">
-        <v>2</v>
-      </c>
-      <c r="Q19" s="8">
-        <v>-46.3</v>
+        <v>2.46</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>-41.1</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B20" s="7">
-        <v>77.900000000000006</v>
+        <v>72.8</v>
       </c>
       <c r="C20" s="7">
-        <v>72.099999999999994</v>
+        <v>76</v>
       </c>
       <c r="D20" s="7">
-        <v>78.3</v>
+        <v>76.2</v>
       </c>
       <c r="E20" s="7">
-        <v>72</v>
+        <v>59.2</v>
       </c>
       <c r="F20" s="8">
-        <v>-5.6</v>
+        <v>3.9</v>
       </c>
       <c r="G20" s="8">
-        <v>-7.21</v>
+        <v>5.41</v>
       </c>
       <c r="H20" s="9">
-        <v>0.56899999999999995</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="I20" s="10">
-        <v>548</v>
-      </c>
-      <c r="J20" s="8">
-        <v>-17.7</v>
+        <v>-8.99</v>
+      </c>
+      <c r="J20" s="10">
+        <v>-18.899999999999999</v>
       </c>
       <c r="K20" s="9">
-        <v>1.48</v>
-      </c>
-      <c r="L20" s="8">
-        <v>-51.9</v>
+        <v>2</v>
+      </c>
+      <c r="L20" s="10">
+        <v>-46.3</v>
       </c>
       <c r="M20" s="9">
-        <v>0.56899999999999995</v>
+        <v>0.51800000000000002</v>
       </c>
       <c r="N20" s="10">
-        <v>548</v>
-      </c>
-      <c r="O20" s="8">
-        <v>-17.7</v>
+        <v>-8.99</v>
+      </c>
+      <c r="O20" s="10">
+        <v>-18.899999999999999</v>
       </c>
       <c r="P20" s="9">
-        <v>1.48</v>
-      </c>
-      <c r="Q20" s="8">
-        <v>-51.9</v>
+        <v>2</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>-46.3</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B21" s="7">
-        <v>81.5</v>
+        <v>77.900000000000006</v>
       </c>
       <c r="C21" s="7">
-        <v>77.7</v>
+        <v>72.099999999999994</v>
       </c>
       <c r="D21" s="7">
-        <v>84.2</v>
+        <v>78.3</v>
       </c>
       <c r="E21" s="7">
-        <v>75.2</v>
-      </c>
-      <c r="F21" s="8">
-        <v>-2.9</v>
-      </c>
-      <c r="G21" s="8">
-        <v>-3.6</v>
+        <v>72</v>
+      </c>
+      <c r="F21" s="10">
+        <v>-5.6</v>
+      </c>
+      <c r="G21" s="10">
+        <v>-7.21</v>
       </c>
       <c r="H21" s="9">
-        <v>8.7800000000000003E-2</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="I21" s="8">
-        <v>-78.7</v>
-      </c>
-      <c r="J21" s="8">
-        <v>-92.6</v>
+        <v>548</v>
+      </c>
+      <c r="J21" s="10">
+        <v>-17.7</v>
       </c>
       <c r="K21" s="9">
-        <v>0.91300000000000003</v>
-      </c>
-      <c r="L21" s="8">
-        <v>-61.8</v>
+        <v>1.48</v>
+      </c>
+      <c r="L21" s="10">
+        <v>-51.9</v>
       </c>
       <c r="M21" s="9">
-        <v>8.7800000000000003E-2</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="N21" s="8">
-        <v>-78.7</v>
-      </c>
-      <c r="O21" s="8">
-        <v>-92.6</v>
+        <v>548</v>
+      </c>
+      <c r="O21" s="10">
+        <v>-17.7</v>
       </c>
       <c r="P21" s="9">
-        <v>0.91300000000000003</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>-61.8</v>
+        <v>1.48</v>
+      </c>
+      <c r="Q21" s="10">
+        <v>-51.9</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B22" s="7">
-        <v>69.099999999999994</v>
+        <v>81.5</v>
       </c>
       <c r="C22" s="7">
-        <v>80.599999999999994</v>
+        <v>77.7</v>
       </c>
       <c r="D22" s="7">
-        <v>83.8</v>
+        <v>84.2</v>
       </c>
       <c r="E22" s="7">
-        <v>68.8</v>
+        <v>75.2</v>
       </c>
       <c r="F22" s="10">
-        <v>10.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G22" s="10">
-        <v>15.31</v>
+        <v>-3.6</v>
       </c>
       <c r="H22" s="9">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="I22" s="8">
-        <v>-0.36</v>
+        <v>8.7800000000000003E-2</v>
+      </c>
+      <c r="I22" s="10">
+        <v>-78.7</v>
       </c>
       <c r="J22" s="10">
-        <v>38.299999999999997</v>
+        <v>-92.6</v>
       </c>
       <c r="K22" s="9">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="L22" s="8">
-        <v>-31.4</v>
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="L22" s="10">
+        <v>-61.8</v>
       </c>
       <c r="M22" s="9">
-        <v>0.41199999999999998</v>
-      </c>
-      <c r="N22" s="8">
-        <v>-0.36</v>
+        <v>8.7800000000000003E-2</v>
+      </c>
+      <c r="N22" s="10">
+        <v>-78.7</v>
       </c>
       <c r="O22" s="10">
-        <v>38.299999999999997</v>
+        <v>-92.6</v>
       </c>
       <c r="P22" s="9">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="Q22" s="8">
-        <v>-31.4</v>
+        <v>0.91300000000000003</v>
+      </c>
+      <c r="Q22" s="10">
+        <v>-61.8</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B23" s="7">
-        <v>84.1</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="C23" s="7">
-        <v>69.900000000000006</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="D23" s="7">
-        <v>85.1</v>
+        <v>83.8</v>
       </c>
       <c r="E23" s="7">
-        <v>69.900000000000006</v>
+        <v>68.8</v>
       </c>
       <c r="F23" s="8">
-        <v>-14.2</v>
+        <v>10.7</v>
       </c>
       <c r="G23" s="8">
-        <v>-16.88</v>
+        <v>15.31</v>
       </c>
       <c r="H23" s="9">
-        <v>0.41299999999999998</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="I23" s="10">
-        <v>2.38</v>
+        <v>-0.36</v>
       </c>
       <c r="J23" s="8">
-        <v>-54.3</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="K23" s="9">
-        <v>0.41299999999999998</v>
-      </c>
-      <c r="L23" s="8">
-        <v>-54.3</v>
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="L23" s="10">
+        <v>-31.4</v>
       </c>
       <c r="M23" s="9">
-        <v>0.41299999999999998</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="N23" s="10">
-        <v>2.38</v>
+        <v>-0.36</v>
       </c>
       <c r="O23" s="8">
-        <v>-54.3</v>
+        <v>38.299999999999997</v>
       </c>
       <c r="P23" s="9">
-        <v>0.41299999999999998</v>
-      </c>
-      <c r="Q23" s="8">
-        <v>-54.3</v>
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="Q23" s="10">
+        <v>-31.4</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B24" s="7">
-        <v>86.8</v>
+        <v>84.1</v>
       </c>
       <c r="C24" s="7">
-        <v>84.1</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="D24" s="7">
-        <v>89.8</v>
+        <v>85.1</v>
       </c>
       <c r="E24" s="7">
-        <v>78.599999999999994</v>
-      </c>
-      <c r="F24" s="8">
-        <v>-2.4</v>
-      </c>
-      <c r="G24" s="8">
-        <v>-2.77</v>
+        <v>69.900000000000006</v>
+      </c>
+      <c r="F24" s="10">
+        <v>-14.2</v>
+      </c>
+      <c r="G24" s="10">
+        <v>-16.88</v>
       </c>
       <c r="H24" s="9">
-        <v>0.40400000000000003</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="I24" s="8">
-        <v>-27.9</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>17</v>
+        <v>2.38</v>
+      </c>
+      <c r="J24" s="10">
+        <v>-54.3</v>
       </c>
       <c r="K24" s="9">
-        <v>7.22</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="L24" s="10">
-        <v>2.6</v>
+        <v>-54.3</v>
       </c>
       <c r="M24" s="9">
-        <v>0.40400000000000003</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="N24" s="8">
-        <v>-27.9</v>
-      </c>
-      <c r="O24" s="9" t="s">
-        <v>17</v>
+        <v>2.38</v>
+      </c>
+      <c r="O24" s="10">
+        <v>-54.3</v>
       </c>
       <c r="P24" s="9">
-        <v>7.22</v>
+        <v>0.41299999999999998</v>
       </c>
       <c r="Q24" s="10">
-        <v>2.6</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B25" s="7">
-        <v>89</v>
+        <v>86.8</v>
       </c>
       <c r="C25" s="7">
-        <v>86.5</v>
+        <v>84.1</v>
       </c>
       <c r="D25" s="7">
-        <v>89</v>
+        <v>89.8</v>
       </c>
       <c r="E25" s="7">
-        <v>86.1</v>
-      </c>
-      <c r="F25" s="8">
-        <v>-2.5</v>
-      </c>
-      <c r="G25" s="8">
-        <v>-2.81</v>
+        <v>78.599999999999994</v>
+      </c>
+      <c r="F25" s="10">
+        <v>-2.4</v>
+      </c>
+      <c r="G25" s="10">
+        <v>-2.77</v>
       </c>
       <c r="H25" s="9">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="I25" s="8">
-        <v>-1.92</v>
-      </c>
-      <c r="J25" s="8">
-        <v>-43.4</v>
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="I25" s="10">
+        <v>-27.9</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K25" s="9">
-        <v>6.82</v>
+        <v>7.22</v>
       </c>
       <c r="L25" s="8">
-        <v>-3.12</v>
+        <v>2.6</v>
       </c>
       <c r="M25" s="9">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="N25" s="8">
-        <v>-1.92</v>
-      </c>
-      <c r="O25" s="8">
-        <v>-43.4</v>
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="N25" s="10">
+        <v>-27.9</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P25" s="9">
-        <v>6.82</v>
+        <v>7.22</v>
       </c>
       <c r="Q25" s="8">
-        <v>-3.12</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B26" s="7">
-        <v>93.7</v>
+        <v>89</v>
       </c>
       <c r="C26" s="7">
+        <v>86.5</v>
+      </c>
+      <c r="D26" s="7">
         <v>89</v>
       </c>
-      <c r="D26" s="7">
-        <v>94.3</v>
-      </c>
       <c r="E26" s="7">
-        <v>85.3</v>
-      </c>
-      <c r="F26" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G26" s="8">
-        <v>-3.26</v>
+        <v>86.1</v>
+      </c>
+      <c r="F26" s="10">
+        <v>-2.5</v>
+      </c>
+      <c r="G26" s="10">
+        <v>-2.81</v>
       </c>
       <c r="H26" s="9">
-        <v>0.57099999999999995</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="I26" s="10">
-        <v>14064.5</v>
-      </c>
-      <c r="J26" s="8">
-        <v>-48</v>
+        <v>-1.92</v>
+      </c>
+      <c r="J26" s="10">
+        <v>-43.4</v>
       </c>
       <c r="K26" s="9">
-        <v>6.26</v>
+        <v>6.82</v>
       </c>
       <c r="L26" s="10">
-        <v>3.44</v>
+        <v>-3.12</v>
       </c>
       <c r="M26" s="9">
-        <v>0.57099999999999995</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="N26" s="10">
-        <v>14064.5</v>
-      </c>
-      <c r="O26" s="8">
-        <v>-48</v>
+        <v>-1.92</v>
+      </c>
+      <c r="O26" s="10">
+        <v>-43.4</v>
       </c>
       <c r="P26" s="9">
-        <v>6.26</v>
+        <v>6.82</v>
       </c>
       <c r="Q26" s="10">
-        <v>3.44</v>
+        <v>-3.12</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B27" s="7">
-        <v>117</v>
+        <v>93.7</v>
       </c>
       <c r="C27" s="7">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D27" s="7">
-        <v>117</v>
+        <v>94.3</v>
       </c>
       <c r="E27" s="7">
-        <v>89.8</v>
-      </c>
-      <c r="F27" s="8">
-        <v>-23</v>
-      </c>
-      <c r="G27" s="8">
-        <v>-20</v>
+        <v>85.3</v>
+      </c>
+      <c r="F27" s="10">
+        <v>-3</v>
+      </c>
+      <c r="G27" s="10">
+        <v>-3.26</v>
       </c>
       <c r="H27" s="9">
-        <v>4.0000000000000001E-3</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="I27" s="8">
-        <v>-99.3</v>
-      </c>
-      <c r="J27" s="8">
-        <v>-99.4</v>
+        <v>14064.5</v>
+      </c>
+      <c r="J27" s="10">
+        <v>-48</v>
       </c>
       <c r="K27" s="9">
-        <v>5.69</v>
-      </c>
-      <c r="L27" s="10">
-        <v>14.8</v>
+        <v>6.26</v>
+      </c>
+      <c r="L27" s="8">
+        <v>3.44</v>
       </c>
       <c r="M27" s="9">
-        <v>4.0000000000000001E-3</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="N27" s="8">
-        <v>-99.3</v>
-      </c>
-      <c r="O27" s="8">
-        <v>-99.4</v>
+        <v>14064.5</v>
+      </c>
+      <c r="O27" s="10">
+        <v>-48</v>
       </c>
       <c r="P27" s="9">
-        <v>5.69</v>
-      </c>
-      <c r="Q27" s="10">
-        <v>14.8</v>
+        <v>6.26</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>3.44</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B28" s="7">
-        <v>87.1</v>
+        <v>117</v>
       </c>
       <c r="C28" s="7">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="D28" s="7">
-        <v>128.5</v>
+        <v>117</v>
       </c>
       <c r="E28" s="7">
-        <v>86.4</v>
+        <v>89.8</v>
       </c>
       <c r="F28" s="10">
-        <v>27.9</v>
+        <v>-23</v>
       </c>
       <c r="G28" s="10">
-        <v>32.03</v>
+        <v>-20</v>
       </c>
       <c r="H28" s="9">
-        <v>0.54600000000000004</v>
-      </c>
-      <c r="I28" s="8">
-        <v>-43</v>
-      </c>
-      <c r="J28" s="8">
-        <v>-36.1</v>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="I28" s="10">
+        <v>-99.3</v>
+      </c>
+      <c r="J28" s="10">
+        <v>-99.4</v>
       </c>
       <c r="K28" s="9">
         <v>5.69</v>
       </c>
-      <c r="L28" s="10">
-        <v>33.6</v>
+      <c r="L28" s="8">
+        <v>14.8</v>
       </c>
       <c r="M28" s="9">
-        <v>0.54600000000000004</v>
-      </c>
-      <c r="N28" s="8">
-        <v>-43</v>
-      </c>
-      <c r="O28" s="8">
-        <v>-36.1</v>
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="N28" s="10">
+        <v>-99.3</v>
+      </c>
+      <c r="O28" s="10">
+        <v>-99.4</v>
       </c>
       <c r="P28" s="9">
         <v>5.69</v>
       </c>
-      <c r="Q28" s="10">
-        <v>33.6</v>
+      <c r="Q28" s="8">
+        <v>14.8</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B29" s="7">
-        <v>90.5</v>
+        <v>87.1</v>
       </c>
       <c r="C29" s="7">
-        <v>87.1</v>
+        <v>115</v>
       </c>
       <c r="D29" s="7">
-        <v>105</v>
+        <v>128.5</v>
       </c>
       <c r="E29" s="7">
-        <v>86.1</v>
+        <v>86.4</v>
       </c>
       <c r="F29" s="8">
-        <v>-2.7</v>
+        <v>27.9</v>
       </c>
       <c r="G29" s="8">
-        <v>-3.01</v>
+        <v>32.03</v>
       </c>
       <c r="H29" s="9">
-        <v>0.95799999999999996</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="I29" s="10">
-        <v>108</v>
+        <v>-43</v>
       </c>
       <c r="J29" s="10">
-        <v>69.900000000000006</v>
+        <v>-36.1</v>
       </c>
       <c r="K29" s="9">
-        <v>5.14</v>
-      </c>
-      <c r="L29" s="10">
-        <v>51.2</v>
+        <v>5.69</v>
+      </c>
+      <c r="L29" s="8">
+        <v>33.6</v>
       </c>
       <c r="M29" s="9">
-        <v>0.95799999999999996</v>
+        <v>0.54600000000000004</v>
       </c>
       <c r="N29" s="10">
-        <v>108</v>
+        <v>-43</v>
       </c>
       <c r="O29" s="10">
-        <v>69.900000000000006</v>
+        <v>-36.1</v>
       </c>
       <c r="P29" s="9">
-        <v>5.14</v>
-      </c>
-      <c r="Q29" s="10">
-        <v>51.2</v>
+        <v>5.69</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>33.6</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B30" s="7">
-        <v>94</v>
+        <v>90.5</v>
       </c>
       <c r="C30" s="7">
-        <v>89.8</v>
+        <v>87.1</v>
       </c>
       <c r="D30" s="7">
-        <v>95.8</v>
+        <v>105</v>
       </c>
       <c r="E30" s="7">
         <v>86.1</v>
       </c>
-      <c r="F30" s="8">
-        <v>-4.7</v>
-      </c>
-      <c r="G30" s="8">
-        <v>-4.97</v>
+      <c r="F30" s="10">
+        <v>-2.7</v>
+      </c>
+      <c r="G30" s="10">
+        <v>-3.01</v>
       </c>
       <c r="H30" s="9">
-        <v>0.46100000000000002</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="I30" s="8">
-        <v>-27.9</v>
+        <v>108</v>
       </c>
       <c r="J30" s="8">
-        <v>-8.77</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="K30" s="9">
-        <v>4.18</v>
-      </c>
-      <c r="L30" s="10">
-        <v>47.4</v>
+        <v>5.14</v>
+      </c>
+      <c r="L30" s="8">
+        <v>51.2</v>
       </c>
       <c r="M30" s="9">
-        <v>0.46100000000000002</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="N30" s="8">
-        <v>-27.9</v>
+        <v>108</v>
       </c>
       <c r="O30" s="8">
-        <v>-8.77</v>
+        <v>69.900000000000006</v>
       </c>
       <c r="P30" s="9">
-        <v>4.18</v>
-      </c>
-      <c r="Q30" s="10">
-        <v>47.4</v>
+        <v>5.14</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>51.2</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B31" s="7">
-        <v>94.5</v>
+        <v>94</v>
       </c>
       <c r="C31" s="7">
-        <v>94.5</v>
+        <v>89.8</v>
       </c>
       <c r="D31" s="7">
-        <v>101.5</v>
+        <v>95.8</v>
       </c>
       <c r="E31" s="7">
-        <v>88.4</v>
-      </c>
-      <c r="F31" s="8">
-        <v>-2.4</v>
-      </c>
-      <c r="G31" s="8">
-        <v>-2.48</v>
+        <v>86.1</v>
+      </c>
+      <c r="F31" s="10">
+        <v>-4.7</v>
+      </c>
+      <c r="G31" s="10">
+        <v>-4.97</v>
       </c>
       <c r="H31" s="9">
-        <v>0.63900000000000001</v>
-      </c>
-      <c r="I31" s="8">
-        <v>-7.6</v>
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="I31" s="10">
+        <v>-27.9</v>
       </c>
       <c r="J31" s="10">
-        <v>1.1399999999999999</v>
+        <v>-8.77</v>
       </c>
       <c r="K31" s="9">
-        <v>3.72</v>
-      </c>
-      <c r="L31" s="10">
-        <v>59.6</v>
+        <v>4.18</v>
+      </c>
+      <c r="L31" s="8">
+        <v>47.4</v>
       </c>
       <c r="M31" s="9">
-        <v>0.63900000000000001</v>
-      </c>
-      <c r="N31" s="8">
-        <v>-7.6</v>
+        <v>0.46100000000000002</v>
+      </c>
+      <c r="N31" s="10">
+        <v>-27.9</v>
       </c>
       <c r="O31" s="10">
-        <v>1.1399999999999999</v>
+        <v>-8.77</v>
       </c>
       <c r="P31" s="9">
-        <v>3.72</v>
-      </c>
-      <c r="Q31" s="10">
-        <v>59.6</v>
+        <v>4.18</v>
+      </c>
+      <c r="Q31" s="8">
+        <v>47.4</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B32" s="7">
-        <v>67.599999999999994</v>
+        <v>94.5</v>
       </c>
       <c r="C32" s="7">
-        <v>96.9</v>
+        <v>94.5</v>
       </c>
       <c r="D32" s="7">
-        <v>98.9</v>
+        <v>101.5</v>
       </c>
       <c r="E32" s="7">
-        <v>66.8</v>
+        <v>88.4</v>
       </c>
       <c r="F32" s="10">
-        <v>29.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G32" s="10">
-        <v>43.34</v>
+        <v>-2.48</v>
       </c>
       <c r="H32" s="9">
-        <v>0.69099999999999995</v>
-      </c>
-      <c r="I32" s="8">
-        <v>-41.9</v>
-      </c>
-      <c r="J32" s="10">
-        <v>65.8</v>
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="I32" s="10">
+        <v>-7.6</v>
+      </c>
+      <c r="J32" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="K32" s="9">
-        <v>3.08</v>
-      </c>
-      <c r="L32" s="10">
-        <v>81.3</v>
+        <v>3.72</v>
+      </c>
+      <c r="L32" s="8">
+        <v>59.6</v>
       </c>
       <c r="M32" s="9">
-        <v>0.69099999999999995</v>
-      </c>
-      <c r="N32" s="8">
-        <v>-41.9</v>
-      </c>
-      <c r="O32" s="10">
-        <v>65.8</v>
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="N32" s="10">
+        <v>-7.6</v>
+      </c>
+      <c r="O32" s="8">
+        <v>1.1399999999999999</v>
       </c>
       <c r="P32" s="9">
-        <v>3.08</v>
-      </c>
-      <c r="Q32" s="10">
-        <v>81.3</v>
+        <v>3.72</v>
+      </c>
+      <c r="Q32" s="8">
+        <v>59.6</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B33" s="7">
-        <v>87</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="C33" s="7">
-        <v>67.599999999999994</v>
+        <v>96.9</v>
       </c>
       <c r="D33" s="7">
-        <v>91.7</v>
+        <v>98.9</v>
       </c>
       <c r="E33" s="7">
-        <v>52.4</v>
+        <v>66.8</v>
       </c>
       <c r="F33" s="8">
-        <v>-21.4</v>
+        <v>29.3</v>
       </c>
       <c r="G33" s="8">
-        <v>-24.04</v>
+        <v>43.34</v>
       </c>
       <c r="H33" s="9">
-        <v>1.19</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="I33" s="10">
-        <v>299.89999999999998</v>
-      </c>
-      <c r="J33" s="10">
-        <v>79.400000000000006</v>
+        <v>-41.9</v>
+      </c>
+      <c r="J33" s="8">
+        <v>65.8</v>
       </c>
       <c r="K33" s="9">
-        <v>2.39</v>
-      </c>
-      <c r="L33" s="10">
-        <v>86.4</v>
+        <v>3.08</v>
+      </c>
+      <c r="L33" s="8">
+        <v>81.3</v>
       </c>
       <c r="M33" s="9">
-        <v>1.19</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="N33" s="10">
-        <v>299.89999999999998</v>
-      </c>
-      <c r="O33" s="10">
-        <v>79.400000000000006</v>
+        <v>-41.9</v>
+      </c>
+      <c r="O33" s="8">
+        <v>65.8</v>
       </c>
       <c r="P33" s="9">
-        <v>2.39</v>
-      </c>
-      <c r="Q33" s="10">
-        <v>86.4</v>
+        <v>3.08</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>81.3</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B34" s="7">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C34" s="7">
-        <v>89</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="D34" s="7">
-        <v>106.5</v>
+        <v>91.7</v>
       </c>
       <c r="E34" s="7">
-        <v>88.6</v>
-      </c>
-      <c r="F34" s="8">
-        <v>-3.5</v>
-      </c>
-      <c r="G34" s="8">
-        <v>-3.78</v>
+        <v>52.4</v>
+      </c>
+      <c r="F34" s="10">
+        <v>-21.4</v>
+      </c>
+      <c r="G34" s="10">
+        <v>-24.04</v>
       </c>
       <c r="H34" s="9">
-        <v>0.29799999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="I34" s="8">
-        <v>-67.099999999999994</v>
-      </c>
-      <c r="J34" s="10">
-        <v>29</v>
+        <v>299.89999999999998</v>
+      </c>
+      <c r="J34" s="8">
+        <v>79.400000000000006</v>
       </c>
       <c r="K34" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="L34" s="10">
-        <v>93.8</v>
+        <v>2.39</v>
+      </c>
+      <c r="L34" s="8">
+        <v>86.4</v>
       </c>
       <c r="M34" s="9">
-        <v>0.29799999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="N34" s="8">
-        <v>-67.099999999999994</v>
-      </c>
-      <c r="O34" s="10">
-        <v>29</v>
+        <v>299.89999999999998</v>
+      </c>
+      <c r="O34" s="8">
+        <v>79.400000000000006</v>
       </c>
       <c r="P34" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="Q34" s="10">
-        <v>93.8</v>
+        <v>2.39</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>86.4</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B35" s="7">
-        <v>99.7</v>
+        <v>92</v>
       </c>
       <c r="C35" s="7">
-        <v>92.5</v>
+        <v>89</v>
       </c>
       <c r="D35" s="7">
-        <v>99.8</v>
+        <v>106.5</v>
       </c>
       <c r="E35" s="7">
-        <v>89</v>
-      </c>
-      <c r="F35" s="8">
-        <v>-6.6</v>
-      </c>
-      <c r="G35" s="8">
-        <v>-6.66</v>
+        <v>88.6</v>
+      </c>
+      <c r="F35" s="10">
+        <v>-3.5</v>
+      </c>
+      <c r="G35" s="10">
+        <v>-3.78</v>
       </c>
       <c r="H35" s="9">
-        <v>0.90400000000000003</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="10">
-        <v>132.19999999999999</v>
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="I35" s="10">
+        <v>-67.099999999999994</v>
+      </c>
+      <c r="J35" s="8">
+        <v>29</v>
       </c>
       <c r="K35" s="9">
-        <v>0.90400000000000003</v>
-      </c>
-      <c r="L35" s="10">
-        <v>132.19999999999999</v>
+        <v>1.2</v>
+      </c>
+      <c r="L35" s="8">
+        <v>93.8</v>
       </c>
       <c r="M35" s="9">
-        <v>0.90400000000000003</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O35" s="10">
-        <v>132.19999999999999</v>
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="N35" s="10">
+        <v>-67.099999999999994</v>
+      </c>
+      <c r="O35" s="8">
+        <v>29</v>
       </c>
       <c r="P35" s="9">
-        <v>0.90400000000000003</v>
-      </c>
-      <c r="Q35" s="10">
-        <v>132.19999999999999</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q35" s="8">
+        <v>93.8</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B36" s="7">
-        <v>137</v>
+        <v>99.7</v>
       </c>
       <c r="C36" s="7">
-        <v>99.1</v>
+        <v>92.5</v>
       </c>
       <c r="D36" s="7">
-        <v>137.5</v>
+        <v>99.8</v>
       </c>
       <c r="E36" s="7">
-        <v>93.3</v>
-      </c>
-      <c r="F36" s="8">
-        <v>-37.4</v>
-      </c>
-      <c r="G36" s="8">
-        <v>-27.4</v>
+        <v>89</v>
+      </c>
+      <c r="F36" s="10">
+        <v>-6.6</v>
+      </c>
+      <c r="G36" s="10">
+        <v>-6.66</v>
       </c>
       <c r="H36" s="9">
-        <v>0</v>
-      </c>
-      <c r="I36" s="8">
-        <v>-100</v>
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J36" s="8">
-        <v>-100</v>
+        <v>132.19999999999999</v>
       </c>
       <c r="K36" s="9">
-        <v>7.04</v>
-      </c>
-      <c r="L36" s="10">
-        <v>192.1</v>
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="L36" s="8">
+        <v>132.19999999999999</v>
       </c>
       <c r="M36" s="9">
-        <v>0</v>
-      </c>
-      <c r="N36" s="8">
-        <v>-100</v>
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O36" s="8">
-        <v>-100</v>
+        <v>132.19999999999999</v>
       </c>
       <c r="P36" s="9">
-        <v>7.04</v>
-      </c>
-      <c r="Q36" s="10">
-        <v>192.1</v>
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>132.19999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B37" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C37" s="7">
-        <v>136.5</v>
+        <v>99.1</v>
       </c>
       <c r="D37" s="7">
-        <v>143</v>
+        <v>137.5</v>
       </c>
       <c r="E37" s="7">
-        <v>130</v>
+        <v>93.3</v>
       </c>
       <c r="F37" s="10">
-        <v>3</v>
+        <v>-37.4</v>
       </c>
       <c r="G37" s="10">
-        <v>2.25</v>
+        <v>-27.4</v>
       </c>
       <c r="H37" s="9">
-        <v>0.98899999999999999</v>
-      </c>
-      <c r="I37" s="8">
-        <v>-9.86</v>
+        <v>0</v>
+      </c>
+      <c r="I37" s="10">
+        <v>-100</v>
       </c>
       <c r="J37" s="10">
-        <v>153.4</v>
+        <v>-100</v>
       </c>
       <c r="K37" s="9">
         <v>7.04</v>
       </c>
-      <c r="L37" s="10">
-        <v>244.9</v>
+      <c r="L37" s="8">
+        <v>192.1</v>
       </c>
       <c r="M37" s="9">
-        <v>0.98899999999999999</v>
-      </c>
-      <c r="N37" s="8">
-        <v>-9.86</v>
+        <v>0</v>
+      </c>
+      <c r="N37" s="10">
+        <v>-100</v>
       </c>
       <c r="O37" s="10">
-        <v>153.4</v>
+        <v>-100</v>
       </c>
       <c r="P37" s="9">
         <v>7.04</v>
       </c>
-      <c r="Q37" s="10">
-        <v>244.9</v>
+      <c r="Q37" s="8">
+        <v>192.1</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B38" s="7">
-        <v>148.5</v>
+        <v>134</v>
       </c>
       <c r="C38" s="7">
-        <v>133.5</v>
+        <v>136.5</v>
       </c>
       <c r="D38" s="7">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E38" s="7">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F38" s="8">
-        <v>-15.5</v>
+        <v>3</v>
       </c>
       <c r="G38" s="8">
-        <v>-10.4</v>
+        <v>2.25</v>
       </c>
       <c r="H38" s="9">
-        <v>1.1000000000000001</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="I38" s="10">
-        <v>56.5</v>
-      </c>
-      <c r="J38" s="10">
-        <v>105.4</v>
+        <v>-9.86</v>
+      </c>
+      <c r="J38" s="8">
+        <v>153.4</v>
       </c>
       <c r="K38" s="9">
-        <v>6.05</v>
-      </c>
-      <c r="L38" s="10">
-        <v>266.5</v>
+        <v>7.04</v>
+      </c>
+      <c r="L38" s="8">
+        <v>244.9</v>
       </c>
       <c r="M38" s="9">
-        <v>1.1000000000000001</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="N38" s="10">
-        <v>56.5</v>
-      </c>
-      <c r="O38" s="10">
-        <v>105.4</v>
+        <v>-9.86</v>
+      </c>
+      <c r="O38" s="8">
+        <v>153.4</v>
       </c>
       <c r="P38" s="9">
-        <v>6.05</v>
-      </c>
-      <c r="Q38" s="10">
-        <v>266.5</v>
+        <v>7.04</v>
+      </c>
+      <c r="Q38" s="8">
+        <v>244.9</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B39" s="7">
         <v>148.5</v>
       </c>
       <c r="C39" s="7">
-        <v>149</v>
+        <v>133.5</v>
       </c>
       <c r="D39" s="7">
-        <v>154.5</v>
+        <v>152</v>
       </c>
       <c r="E39" s="7">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="F39" s="10">
-        <v>3</v>
+        <v>-15.5</v>
       </c>
       <c r="G39" s="10">
-        <v>2.0499999999999998</v>
+        <v>-10.4</v>
       </c>
       <c r="H39" s="9">
-        <v>0.70099999999999996</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I39" s="8">
-        <v>-18</v>
-      </c>
-      <c r="J39" s="10">
-        <v>89.3</v>
+        <v>56.5</v>
+      </c>
+      <c r="J39" s="8">
+        <v>105.4</v>
       </c>
       <c r="K39" s="9">
-        <v>4.96</v>
-      </c>
-      <c r="L39" s="10">
-        <v>343.5</v>
+        <v>6.05</v>
+      </c>
+      <c r="L39" s="8">
+        <v>266.5</v>
       </c>
       <c r="M39" s="9">
-        <v>0.70099999999999996</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N39" s="8">
-        <v>-18</v>
-      </c>
-      <c r="O39" s="10">
-        <v>89.3</v>
+        <v>56.5</v>
+      </c>
+      <c r="O39" s="8">
+        <v>105.4</v>
       </c>
       <c r="P39" s="9">
-        <v>4.96</v>
-      </c>
-      <c r="Q39" s="10">
-        <v>343.5</v>
+        <v>6.05</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>266.5</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B40" s="7">
-        <v>165</v>
+        <v>148.5</v>
       </c>
       <c r="C40" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D40" s="7">
-        <v>167.5</v>
+        <v>154.5</v>
       </c>
       <c r="E40" s="7">
-        <v>137.5</v>
+        <v>145</v>
       </c>
       <c r="F40" s="8">
-        <v>-21</v>
+        <v>3</v>
       </c>
       <c r="G40" s="8">
-        <v>-12.57</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="H40" s="9">
-        <v>0.85399999999999998</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="I40" s="10">
-        <v>51.4</v>
-      </c>
-      <c r="J40" s="10">
-        <v>266.60000000000002</v>
+        <v>-18</v>
+      </c>
+      <c r="J40" s="8">
+        <v>89.3</v>
       </c>
       <c r="K40" s="9">
-        <v>4.26</v>
-      </c>
-      <c r="L40" s="10">
-        <v>469.4</v>
+        <v>4.96</v>
+      </c>
+      <c r="L40" s="8">
+        <v>343.5</v>
       </c>
       <c r="M40" s="9">
-        <v>0.85399999999999998</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="N40" s="10">
-        <v>51.4</v>
-      </c>
-      <c r="O40" s="10">
-        <v>266.60000000000002</v>
+        <v>-18</v>
+      </c>
+      <c r="O40" s="8">
+        <v>89.3</v>
       </c>
       <c r="P40" s="9">
-        <v>4.26</v>
-      </c>
-      <c r="Q40" s="10">
-        <v>469.4</v>
+        <v>4.96</v>
+      </c>
+      <c r="Q40" s="8">
+        <v>343.5</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B41" s="7">
-        <v>160.5</v>
+        <v>165</v>
       </c>
       <c r="C41" s="7">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="D41" s="7">
-        <v>172.5</v>
+        <v>167.5</v>
       </c>
       <c r="E41" s="7">
-        <v>158.5</v>
+        <v>137.5</v>
       </c>
       <c r="F41" s="10">
-        <v>8</v>
+        <v>-21</v>
       </c>
       <c r="G41" s="10">
-        <v>5.03</v>
+        <v>-12.57</v>
       </c>
       <c r="H41" s="9">
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="I41" s="10">
-        <v>11.7</v>
-      </c>
-      <c r="J41" s="10">
-        <v>333.5</v>
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="I41" s="8">
+        <v>51.4</v>
+      </c>
+      <c r="J41" s="8">
+        <v>266.60000000000002</v>
       </c>
       <c r="K41" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="L41" s="10">
-        <v>561.29999999999995</v>
+        <v>4.26</v>
+      </c>
+      <c r="L41" s="8">
+        <v>469.4</v>
       </c>
       <c r="M41" s="9">
-        <v>0.56399999999999995</v>
-      </c>
-      <c r="N41" s="10">
-        <v>11.7</v>
-      </c>
-      <c r="O41" s="10">
-        <v>333.5</v>
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="N41" s="8">
+        <v>51.4</v>
+      </c>
+      <c r="O41" s="8">
+        <v>266.60000000000002</v>
       </c>
       <c r="P41" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="Q41" s="10">
-        <v>561.29999999999995</v>
+        <v>4.26</v>
+      </c>
+      <c r="Q41" s="8">
+        <v>469.4</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B42" s="7">
-        <v>139</v>
+        <v>160.5</v>
       </c>
       <c r="C42" s="7">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D42" s="7">
-        <v>165</v>
+        <v>172.5</v>
       </c>
       <c r="E42" s="7">
-        <v>137</v>
-      </c>
-      <c r="F42" s="10">
-        <v>20</v>
-      </c>
-      <c r="G42" s="10">
-        <v>14.39</v>
+        <v>158.5</v>
+      </c>
+      <c r="F42" s="8">
+        <v>8</v>
+      </c>
+      <c r="G42" s="8">
+        <v>5.03</v>
       </c>
       <c r="H42" s="9">
-        <v>0.505</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="I42" s="8">
-        <v>-20</v>
-      </c>
-      <c r="J42" s="10">
-        <v>590.70000000000005</v>
+        <v>11.7</v>
+      </c>
+      <c r="J42" s="8">
+        <v>333.5</v>
       </c>
       <c r="K42" s="9">
-        <v>2.84</v>
-      </c>
-      <c r="L42" s="10">
-        <v>638.4</v>
+        <v>3.4</v>
+      </c>
+      <c r="L42" s="8">
+        <v>561.29999999999995</v>
       </c>
       <c r="M42" s="9">
-        <v>0.505</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="N42" s="8">
-        <v>-20</v>
-      </c>
-      <c r="O42" s="10">
-        <v>590.70000000000005</v>
+        <v>11.7</v>
+      </c>
+      <c r="O42" s="8">
+        <v>333.5</v>
       </c>
       <c r="P42" s="9">
-        <v>2.84</v>
-      </c>
-      <c r="Q42" s="10">
-        <v>638.4</v>
+        <v>3.4</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>561.29999999999995</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B43" s="7">
-        <v>158.5</v>
+        <v>139</v>
       </c>
       <c r="C43" s="7">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D43" s="7">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E43" s="7">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F43" s="8">
-        <v>-18</v>
+        <v>20</v>
       </c>
       <c r="G43" s="8">
-        <v>-11.46</v>
+        <v>14.39</v>
       </c>
       <c r="H43" s="9">
-        <v>0.63100000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="I43" s="10">
-        <v>51.4</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>17</v>
+        <v>-20</v>
+      </c>
+      <c r="J43" s="8">
+        <v>590.70000000000005</v>
       </c>
       <c r="K43" s="9">
-        <v>2.33</v>
-      </c>
-      <c r="L43" s="10">
-        <v>649.6</v>
+        <v>2.84</v>
+      </c>
+      <c r="L43" s="8">
+        <v>638.4</v>
       </c>
       <c r="M43" s="9">
-        <v>0.63100000000000001</v>
+        <v>0.505</v>
       </c>
       <c r="N43" s="10">
-        <v>51.4</v>
-      </c>
-      <c r="O43" s="9" t="s">
-        <v>17</v>
+        <v>-20</v>
+      </c>
+      <c r="O43" s="8">
+        <v>590.70000000000005</v>
       </c>
       <c r="P43" s="9">
-        <v>2.33</v>
-      </c>
-      <c r="Q43" s="10">
-        <v>649.6</v>
+        <v>2.84</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>638.4</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B44" s="7">
-        <v>168.5</v>
+        <v>158.5</v>
       </c>
       <c r="C44" s="7">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="D44" s="7">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="E44" s="7">
-        <v>155</v>
-      </c>
-      <c r="F44" s="8">
-        <v>-11</v>
-      </c>
-      <c r="G44" s="8">
-        <v>-6.55</v>
+        <v>130</v>
+      </c>
+      <c r="F44" s="10">
+        <v>-18</v>
+      </c>
+      <c r="G44" s="10">
+        <v>-11.46</v>
       </c>
       <c r="H44" s="9">
-        <v>0.41699999999999998</v>
+        <v>0.63100000000000001</v>
       </c>
       <c r="I44" s="8">
-        <v>-37.1</v>
-      </c>
-      <c r="J44" s="10">
-        <v>34.1</v>
+        <v>51.4</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K44" s="9">
-        <v>1.7</v>
-      </c>
-      <c r="L44" s="10">
-        <v>446.6</v>
+        <v>2.33</v>
+      </c>
+      <c r="L44" s="8">
+        <v>649.6</v>
       </c>
       <c r="M44" s="9">
-        <v>0.41699999999999998</v>
+        <v>0.63100000000000001</v>
       </c>
       <c r="N44" s="8">
-        <v>-37.1</v>
-      </c>
-      <c r="O44" s="10">
-        <v>34.1</v>
+        <v>51.4</v>
+      </c>
+      <c r="O44" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P44" s="9">
-        <v>1.7</v>
-      </c>
-      <c r="Q44" s="10">
-        <v>446.6</v>
+        <v>2.33</v>
+      </c>
+      <c r="Q44" s="8">
+        <v>649.6</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B45" s="7">
-        <v>184</v>
+        <v>168.5</v>
       </c>
       <c r="C45" s="7">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D45" s="7">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="E45" s="7">
-        <v>166.5</v>
-      </c>
-      <c r="F45" s="8">
-        <v>-13.5</v>
-      </c>
-      <c r="G45" s="8">
-        <v>-7.44</v>
+        <v>155</v>
+      </c>
+      <c r="F45" s="10">
+        <v>-11</v>
+      </c>
+      <c r="G45" s="10">
+        <v>-6.55</v>
       </c>
       <c r="H45" s="9">
-        <v>0.66300000000000003</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="I45" s="10">
-        <v>187.6</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>17</v>
+        <v>-37.1</v>
+      </c>
+      <c r="J45" s="8">
+        <v>34.1</v>
       </c>
       <c r="K45" s="9">
-        <v>1.28</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>17</v>
+        <v>1.7</v>
+      </c>
+      <c r="L45" s="8">
+        <v>446.6</v>
       </c>
       <c r="M45" s="9">
-        <v>0.66300000000000003</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="N45" s="10">
-        <v>187.6</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>17</v>
+        <v>-37.1</v>
+      </c>
+      <c r="O45" s="8">
+        <v>34.1</v>
       </c>
       <c r="P45" s="9">
-        <v>1.28</v>
-      </c>
-      <c r="Q45" s="9" t="s">
-        <v>17</v>
+        <v>1.7</v>
+      </c>
+      <c r="Q45" s="8">
+        <v>446.6</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B46" s="7">
-        <v>170.5</v>
+        <v>184</v>
       </c>
       <c r="C46" s="7">
-        <v>181.5</v>
+        <v>168</v>
       </c>
       <c r="D46" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E46" s="7">
-        <v>165</v>
+        <v>166.5</v>
       </c>
       <c r="F46" s="10">
-        <v>13</v>
+        <v>-13.5</v>
       </c>
       <c r="G46" s="10">
-        <v>7.72</v>
+        <v>-7.44</v>
       </c>
       <c r="H46" s="9">
-        <v>0.23100000000000001</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="I46" s="8">
-        <v>-40.799999999999997</v>
+        <v>187.6</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K46" s="9">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="L46" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M46" s="9">
-        <v>0.23100000000000001</v>
+        <v>0.66300000000000003</v>
       </c>
       <c r="N46" s="8">
-        <v>-40.799999999999997</v>
+        <v>187.6</v>
       </c>
       <c r="O46" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P46" s="9">
-        <v>0.62</v>
+        <v>1.28</v>
       </c>
       <c r="Q46" s="9" t="s">
         <v>17</v>
@@ -3609,52 +3617,52 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B47" s="7">
-        <v>168</v>
+        <v>170.5</v>
       </c>
       <c r="C47" s="7">
-        <v>168.5</v>
+        <v>181.5</v>
       </c>
       <c r="D47" s="7">
-        <v>189.5</v>
+        <v>185</v>
       </c>
       <c r="E47" s="7">
-        <v>163</v>
-      </c>
-      <c r="F47" s="10">
-        <v>3</v>
-      </c>
-      <c r="G47" s="10">
-        <v>1.81</v>
+        <v>165</v>
+      </c>
+      <c r="F47" s="8">
+        <v>13</v>
+      </c>
+      <c r="G47" s="8">
+        <v>7.72</v>
       </c>
       <c r="H47" s="9">
-        <v>0.38900000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="I47" s="10">
-        <v>5.56</v>
+        <v>-40.799999999999997</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K47" s="9">
-        <v>0.38900000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="L47" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M47" s="9">
-        <v>0.38900000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="N47" s="10">
-        <v>5.56</v>
+        <v>-40.799999999999997</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P47" s="9">
-        <v>0.38900000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="Q47" s="9" t="s">
         <v>17</v>
@@ -3662,555 +3670,555 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B48" s="7">
-        <v>166.5</v>
+        <v>168</v>
       </c>
       <c r="C48" s="7">
-        <v>165.5</v>
+        <v>168.5</v>
       </c>
       <c r="D48" s="7">
-        <v>176</v>
+        <v>189.5</v>
       </c>
       <c r="E48" s="7">
-        <v>146.5</v>
-      </c>
-      <c r="F48" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="G48" s="10">
-        <v>2.8</v>
+        <v>163</v>
+      </c>
+      <c r="F48" s="8">
+        <v>3</v>
+      </c>
+      <c r="G48" s="8">
+        <v>1.81</v>
       </c>
       <c r="H48" s="9">
-        <v>0.36899999999999999</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="I48" s="8">
-        <v>-5.43</v>
-      </c>
-      <c r="J48" s="10">
-        <v>4499.2</v>
+        <v>5.56</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K48" s="9">
-        <v>2.41</v>
-      </c>
-      <c r="L48" s="10">
-        <v>2757.3</v>
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M48" s="9">
-        <v>0.36899999999999999</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="N48" s="8">
-        <v>-5.43</v>
-      </c>
-      <c r="O48" s="10">
-        <v>4499.2</v>
+        <v>5.56</v>
+      </c>
+      <c r="O48" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P48" s="9">
-        <v>2.41</v>
-      </c>
-      <c r="Q48" s="10">
-        <v>2757.3</v>
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="Q48" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B49" s="7">
-        <v>193</v>
+        <v>166.5</v>
       </c>
       <c r="C49" s="7">
-        <v>161</v>
+        <v>165.5</v>
       </c>
       <c r="D49" s="7">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="E49" s="7">
-        <v>139.5</v>
+        <v>146.5</v>
       </c>
       <c r="F49" s="8">
-        <v>-32</v>
+        <v>4.5</v>
       </c>
       <c r="G49" s="8">
-        <v>-16.579999999999998</v>
+        <v>2.8</v>
       </c>
       <c r="H49" s="9">
-        <v>0.39</v>
-      </c>
-      <c r="I49" s="8">
-        <v>-27</v>
-      </c>
-      <c r="J49" s="10">
-        <v>4763.7</v>
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="I49" s="10">
+        <v>-5.43</v>
+      </c>
+      <c r="J49" s="8">
+        <v>4499.2</v>
       </c>
       <c r="K49" s="9">
-        <v>2.04</v>
-      </c>
-      <c r="L49" s="10">
-        <v>2574.3000000000002</v>
+        <v>2.41</v>
+      </c>
+      <c r="L49" s="8">
+        <v>2757.3</v>
       </c>
       <c r="M49" s="9">
-        <v>0.39</v>
-      </c>
-      <c r="N49" s="8">
-        <v>-27</v>
-      </c>
-      <c r="O49" s="10">
-        <v>4763.7</v>
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="N49" s="10">
+        <v>-5.43</v>
+      </c>
+      <c r="O49" s="8">
+        <v>4499.2</v>
       </c>
       <c r="P49" s="9">
-        <v>2.04</v>
-      </c>
-      <c r="Q49" s="10">
-        <v>2574.3000000000002</v>
+        <v>2.41</v>
+      </c>
+      <c r="Q49" s="8">
+        <v>2757.3</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B50" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C50" s="7">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="D50" s="7">
-        <v>224.5</v>
+        <v>201</v>
       </c>
       <c r="E50" s="7">
-        <v>182.5</v>
+        <v>139.5</v>
       </c>
       <c r="F50" s="10">
-        <v>4.5</v>
+        <v>-32</v>
       </c>
       <c r="G50" s="10">
-        <v>2.39</v>
+        <v>-16.579999999999998</v>
       </c>
       <c r="H50" s="9">
-        <v>0.53400000000000003</v>
+        <v>0.39</v>
       </c>
       <c r="I50" s="10">
-        <v>44.3</v>
-      </c>
-      <c r="J50" s="10">
-        <v>6558.6</v>
+        <v>-27</v>
+      </c>
+      <c r="J50" s="8">
+        <v>4763.7</v>
       </c>
       <c r="K50" s="9">
-        <v>1.65</v>
-      </c>
-      <c r="L50" s="10">
-        <v>2317.1999999999998</v>
+        <v>2.04</v>
+      </c>
+      <c r="L50" s="8">
+        <v>2574.3000000000002</v>
       </c>
       <c r="M50" s="9">
-        <v>0.53400000000000003</v>
+        <v>0.39</v>
       </c>
       <c r="N50" s="10">
-        <v>44.3</v>
-      </c>
-      <c r="O50" s="10">
-        <v>6558.6</v>
+        <v>-27</v>
+      </c>
+      <c r="O50" s="8">
+        <v>4763.7</v>
       </c>
       <c r="P50" s="9">
-        <v>1.65</v>
-      </c>
-      <c r="Q50" s="10">
-        <v>2317.1999999999998</v>
+        <v>2.04</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>2574.3000000000002</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B51" s="7">
-        <v>228.5</v>
+        <v>190</v>
       </c>
       <c r="C51" s="7">
-        <v>188.5</v>
+        <v>193</v>
       </c>
       <c r="D51" s="7">
-        <v>229</v>
+        <v>224.5</v>
       </c>
       <c r="E51" s="7">
-        <v>180</v>
+        <v>182.5</v>
       </c>
       <c r="F51" s="8">
-        <v>-40</v>
+        <v>4.5</v>
       </c>
       <c r="G51" s="8">
-        <v>-17.510000000000002</v>
+        <v>2.39</v>
       </c>
       <c r="H51" s="9">
-        <v>0.37</v>
-      </c>
-      <c r="I51" s="10">
-        <v>58.8</v>
-      </c>
-      <c r="J51" s="10">
-        <v>4514.8</v>
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="I51" s="8">
+        <v>44.3</v>
+      </c>
+      <c r="J51" s="8">
+        <v>6558.6</v>
       </c>
       <c r="K51" s="9">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="L51" s="10">
-        <v>1753.2</v>
+        <v>1.65</v>
+      </c>
+      <c r="L51" s="8">
+        <v>2317.1999999999998</v>
       </c>
       <c r="M51" s="9">
-        <v>0.37</v>
-      </c>
-      <c r="N51" s="10">
-        <v>58.8</v>
-      </c>
-      <c r="O51" s="10">
-        <v>4514.8</v>
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="N51" s="8">
+        <v>44.3</v>
+      </c>
+      <c r="O51" s="8">
+        <v>6558.6</v>
       </c>
       <c r="P51" s="9">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="Q51" s="10">
-        <v>1753.2</v>
+        <v>1.65</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>2317.1999999999998</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B52" s="7">
-        <v>261.5</v>
+        <v>228.5</v>
       </c>
       <c r="C52" s="7">
-        <v>228.5</v>
+        <v>188.5</v>
       </c>
       <c r="D52" s="7">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="E52" s="7">
-        <v>220.5</v>
-      </c>
-      <c r="F52" s="8">
-        <v>-27.5</v>
-      </c>
-      <c r="G52" s="8">
-        <v>-10.74</v>
+        <v>180</v>
+      </c>
+      <c r="F52" s="10">
+        <v>-40</v>
+      </c>
+      <c r="G52" s="10">
+        <v>-17.510000000000002</v>
       </c>
       <c r="H52" s="9">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="I52" s="10">
-        <v>79.099999999999994</v>
-      </c>
-      <c r="J52" s="10">
-        <v>2805.9</v>
+        <v>0.37</v>
+      </c>
+      <c r="I52" s="8">
+        <v>58.8</v>
+      </c>
+      <c r="J52" s="8">
+        <v>4514.8</v>
       </c>
       <c r="K52" s="9">
-        <v>0.747</v>
-      </c>
-      <c r="L52" s="10">
-        <v>1329.5</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="L52" s="8">
+        <v>1753.2</v>
       </c>
       <c r="M52" s="9">
-        <v>0.23300000000000001</v>
-      </c>
-      <c r="N52" s="10">
-        <v>79.099999999999994</v>
-      </c>
-      <c r="O52" s="10">
-        <v>2805.9</v>
+        <v>0.37</v>
+      </c>
+      <c r="N52" s="8">
+        <v>58.8</v>
+      </c>
+      <c r="O52" s="8">
+        <v>4514.8</v>
       </c>
       <c r="P52" s="9">
-        <v>0.747</v>
-      </c>
-      <c r="Q52" s="10">
-        <v>1329.5</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>1753.2</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B53" s="7">
-        <v>318</v>
+        <v>261.5</v>
       </c>
       <c r="C53" s="7">
-        <v>256</v>
+        <v>228.5</v>
       </c>
       <c r="D53" s="7">
-        <v>328</v>
+        <v>273</v>
       </c>
       <c r="E53" s="7">
-        <v>236</v>
-      </c>
-      <c r="F53" s="8">
-        <v>-56</v>
-      </c>
-      <c r="G53" s="8">
-        <v>-17.95</v>
+        <v>220.5</v>
+      </c>
+      <c r="F53" s="10">
+        <v>-27.5</v>
+      </c>
+      <c r="G53" s="10">
+        <v>-10.74</v>
       </c>
       <c r="H53" s="9">
-        <v>0.13</v>
-      </c>
-      <c r="I53" s="10">
-        <v>78</v>
-      </c>
-      <c r="J53" s="10">
-        <v>1522.6</v>
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="I53" s="8">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="J53" s="8">
+        <v>2805.9</v>
       </c>
       <c r="K53" s="9">
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="L53" s="10">
-        <v>1062</v>
+        <v>0.747</v>
+      </c>
+      <c r="L53" s="8">
+        <v>1329.5</v>
       </c>
       <c r="M53" s="9">
-        <v>0.13</v>
-      </c>
-      <c r="N53" s="10">
-        <v>78</v>
-      </c>
-      <c r="O53" s="10">
-        <v>1522.6</v>
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="N53" s="8">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="O53" s="8">
+        <v>2805.9</v>
       </c>
       <c r="P53" s="9">
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="Q53" s="10">
-        <v>1062</v>
+        <v>0.747</v>
+      </c>
+      <c r="Q53" s="8">
+        <v>1329.5</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B54" s="7">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C54" s="7">
-        <v>312</v>
+        <v>256</v>
       </c>
       <c r="D54" s="7">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E54" s="7">
-        <v>288.5</v>
-      </c>
-      <c r="F54" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G54" s="8">
-        <v>-0.95</v>
+        <v>236</v>
+      </c>
+      <c r="F54" s="10">
+        <v>-56</v>
+      </c>
+      <c r="G54" s="10">
+        <v>-17.95</v>
       </c>
       <c r="H54" s="9">
-        <v>7.3099999999999998E-2</v>
-      </c>
-      <c r="I54" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="10">
-        <v>811.6</v>
+        <v>0.13</v>
+      </c>
+      <c r="I54" s="8">
+        <v>78</v>
+      </c>
+      <c r="J54" s="8">
+        <v>1522.6</v>
       </c>
       <c r="K54" s="9">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="L54" s="10">
-        <v>960</v>
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="L54" s="8">
+        <v>1062</v>
       </c>
       <c r="M54" s="9">
-        <v>7.3099999999999998E-2</v>
-      </c>
-      <c r="N54" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O54" s="10">
-        <v>811.6</v>
+        <v>0.13</v>
+      </c>
+      <c r="N54" s="8">
+        <v>78</v>
+      </c>
+      <c r="O54" s="8">
+        <v>1522.6</v>
       </c>
       <c r="P54" s="9">
-        <v>0.38400000000000001</v>
-      </c>
-      <c r="Q54" s="10">
-        <v>960</v>
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="Q54" s="8">
+        <v>1062</v>
       </c>
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B55" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C55" s="7">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D55" s="7">
-        <v>349.5</v>
+        <v>324</v>
       </c>
       <c r="E55" s="7">
-        <v>306</v>
+        <v>288.5</v>
       </c>
       <c r="F55" s="10">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="G55" s="10">
-        <v>1.61</v>
+        <v>-0.95</v>
       </c>
       <c r="H55" s="9">
-        <v>0</v>
-      </c>
-      <c r="I55" s="8">
-        <v>-100</v>
+        <v>7.3099999999999998E-2</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J55" s="8">
-        <v>-100</v>
+        <v>811.6</v>
       </c>
       <c r="K55" s="9">
-        <v>0.311</v>
-      </c>
-      <c r="L55" s="10">
-        <v>1002.6</v>
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="L55" s="8">
+        <v>960</v>
       </c>
       <c r="M55" s="9">
-        <v>0</v>
-      </c>
-      <c r="N55" s="8">
-        <v>-100</v>
+        <v>7.3099999999999998E-2</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O55" s="8">
-        <v>-100</v>
+        <v>811.6</v>
       </c>
       <c r="P55" s="9">
-        <v>0.311</v>
-      </c>
-      <c r="Q55" s="10">
-        <v>1002.6</v>
+        <v>0.38400000000000001</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>960</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B56" s="7">
-        <v>254</v>
+        <v>319</v>
       </c>
       <c r="C56" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="D56" s="7">
-        <v>317</v>
+        <v>349.5</v>
       </c>
       <c r="E56" s="7">
-        <v>234.5</v>
-      </c>
-      <c r="F56" s="10">
-        <v>61</v>
-      </c>
-      <c r="G56" s="10">
-        <v>24.5</v>
+        <v>306</v>
+      </c>
+      <c r="F56" s="8">
+        <v>5</v>
+      </c>
+      <c r="G56" s="8">
+        <v>1.61</v>
       </c>
       <c r="H56" s="9">
-        <v>0.311</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I56" s="10">
+        <v>-100</v>
       </c>
       <c r="J56" s="10">
-        <v>3778.4</v>
+        <v>-100</v>
       </c>
       <c r="K56" s="9">
         <v>0.311</v>
       </c>
-      <c r="L56" s="10">
-        <v>1440.6</v>
+      <c r="L56" s="8">
+        <v>1002.6</v>
       </c>
       <c r="M56" s="9">
-        <v>0.311</v>
-      </c>
-      <c r="N56" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N56" s="10">
+        <v>-100</v>
       </c>
       <c r="O56" s="10">
-        <v>3778.4</v>
+        <v>-100</v>
       </c>
       <c r="P56" s="9">
         <v>0.311</v>
       </c>
-      <c r="Q56" s="10">
-        <v>1440.6</v>
+      <c r="Q56" s="8">
+        <v>1002.6</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B57" s="7">
-        <v>199.5</v>
+        <v>254</v>
       </c>
       <c r="C57" s="7">
-        <v>249</v>
+        <v>310</v>
       </c>
       <c r="D57" s="7">
-        <v>257</v>
+        <v>317</v>
       </c>
       <c r="E57" s="7">
-        <v>198</v>
-      </c>
-      <c r="F57" s="10">
-        <v>47</v>
-      </c>
-      <c r="G57" s="10">
-        <v>23.27</v>
+        <v>234.5</v>
+      </c>
+      <c r="F57" s="8">
+        <v>61</v>
+      </c>
+      <c r="G57" s="8">
+        <v>24.5</v>
       </c>
       <c r="H57" s="9">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="I57" s="9" t="s">
         <v>17</v>
       </c>
       <c r="J57" s="8">
-        <v>-100</v>
+        <v>3778.4</v>
       </c>
       <c r="K57" s="9">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="L57" s="8">
-        <v>-100</v>
+        <v>1440.6</v>
       </c>
       <c r="M57" s="9">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>17</v>
       </c>
       <c r="O57" s="8">
-        <v>-100</v>
+        <v>3778.4</v>
       </c>
       <c r="P57" s="9">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="Q57" s="8">
-        <v>-100</v>
+        <v>1440.6</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B58" s="7">
-        <v>201.5</v>
+        <v>199.5</v>
       </c>
       <c r="C58" s="7">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="D58" s="7">
-        <v>208</v>
+        <v>257</v>
       </c>
       <c r="E58" s="7">
-        <v>175</v>
-      </c>
-      <c r="F58" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="G58" s="10">
-        <v>0.75</v>
+        <v>198</v>
+      </c>
+      <c r="F58" s="8">
+        <v>47</v>
+      </c>
+      <c r="G58" s="8">
+        <v>23.27</v>
       </c>
       <c r="H58" s="9">
         <v>0</v>
@@ -4218,13 +4226,13 @@
       <c r="I58" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J58" s="8">
+      <c r="J58" s="10">
         <v>-100</v>
       </c>
       <c r="K58" s="9">
         <v>0</v>
       </c>
-      <c r="L58" s="8">
+      <c r="L58" s="10">
         <v>-100</v>
       </c>
       <c r="M58" s="9">
@@ -4233,143 +4241,143 @@
       <c r="N58" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O58" s="8">
+      <c r="O58" s="10">
         <v>-100</v>
       </c>
       <c r="P58" s="9">
         <v>0</v>
       </c>
-      <c r="Q58" s="8">
+      <c r="Q58" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B59" s="7">
-        <v>185</v>
+        <v>201.5</v>
       </c>
       <c r="C59" s="7">
-        <v>200.5</v>
+        <v>202</v>
       </c>
       <c r="D59" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E59" s="7">
-        <v>184</v>
-      </c>
-      <c r="F59" s="10">
-        <v>15.5</v>
-      </c>
-      <c r="G59" s="10">
-        <v>8.3800000000000008</v>
+        <v>175</v>
+      </c>
+      <c r="F59" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0.75</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
       </c>
-      <c r="I59" s="8">
+      <c r="I59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="10">
         <v>-100</v>
       </c>
-      <c r="J59" s="8">
+      <c r="K59" s="9">
+        <v>0</v>
+      </c>
+      <c r="L59" s="10">
         <v>-100</v>
       </c>
-      <c r="K59" s="9">
-        <v>0</v>
-      </c>
-      <c r="L59" s="8">
+      <c r="M59" s="9">
+        <v>0</v>
+      </c>
+      <c r="N59" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O59" s="10">
         <v>-100</v>
       </c>
-      <c r="M59" s="9">
-        <v>0</v>
-      </c>
-      <c r="N59" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O59" s="8">
-        <v>-100</v>
-      </c>
       <c r="P59" s="9">
         <v>0</v>
       </c>
-      <c r="Q59" s="8">
+      <c r="Q59" s="10">
         <v>-100</v>
       </c>
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B60" s="7">
         <v>185</v>
       </c>
       <c r="C60" s="7">
-        <v>185</v>
+        <v>200.5</v>
       </c>
       <c r="D60" s="7">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="E60" s="7">
-        <v>168.5</v>
-      </c>
-      <c r="F60" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="G60" s="10">
-        <v>0.82</v>
+        <v>184</v>
+      </c>
+      <c r="F60" s="8">
+        <v>15.5</v>
+      </c>
+      <c r="G60" s="8">
+        <v>8.3800000000000008</v>
       </c>
       <c r="H60" s="9">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I60" s="9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I60" s="10">
+        <v>-100</v>
       </c>
       <c r="J60" s="10">
-        <v>285.60000000000002</v>
+        <v>-100</v>
       </c>
       <c r="K60" s="9">
-        <v>8.4400000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="L60" s="10">
-        <v>306.39999999999998</v>
+        <v>-100</v>
       </c>
       <c r="M60" s="9">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="N60" s="9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N60" s="10">
+        <v>-100</v>
       </c>
       <c r="O60" s="10">
-        <v>285.60000000000002</v>
+        <v>-100</v>
       </c>
       <c r="P60" s="9">
-        <v>8.4400000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="Q60" s="10">
-        <v>306.39999999999998</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B61" s="7">
-        <v>222.5</v>
+        <v>185</v>
       </c>
       <c r="C61" s="7">
-        <v>183.5</v>
+        <v>185</v>
       </c>
       <c r="D61" s="7">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="E61" s="7">
-        <v>181.5</v>
+        <v>168.5</v>
       </c>
       <c r="F61" s="8">
-        <v>-35</v>
+        <v>1.5</v>
       </c>
       <c r="G61" s="8">
-        <v>-16.02</v>
+        <v>0.82</v>
       </c>
       <c r="H61" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4377,14 +4385,14 @@
       <c r="I61" s="9">
         <v>0</v>
       </c>
-      <c r="J61" s="10">
+      <c r="J61" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="K61" s="9">
-        <v>7.6300000000000007E-2</v>
-      </c>
-      <c r="L61" s="10">
-        <v>308.7</v>
+        <v>8.4400000000000003E-2</v>
+      </c>
+      <c r="L61" s="8">
+        <v>306.39999999999998</v>
       </c>
       <c r="M61" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4392,37 +4400,37 @@
       <c r="N61" s="9">
         <v>0</v>
       </c>
-      <c r="O61" s="10">
+      <c r="O61" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="P61" s="9">
-        <v>7.6300000000000007E-2</v>
-      </c>
-      <c r="Q61" s="10">
-        <v>308.7</v>
+        <v>8.4400000000000003E-2</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>306.39999999999998</v>
       </c>
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B62" s="7">
-        <v>201.5</v>
+        <v>222.5</v>
       </c>
       <c r="C62" s="7">
-        <v>218.5</v>
+        <v>183.5</v>
       </c>
       <c r="D62" s="7">
-        <v>226.5</v>
+        <v>225</v>
       </c>
       <c r="E62" s="7">
-        <v>196</v>
+        <v>181.5</v>
       </c>
       <c r="F62" s="10">
-        <v>18.5</v>
+        <v>-35</v>
       </c>
       <c r="G62" s="10">
-        <v>9.25</v>
+        <v>-16.02</v>
       </c>
       <c r="H62" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4430,14 +4438,14 @@
       <c r="I62" s="9">
         <v>0</v>
       </c>
-      <c r="J62" s="10">
+      <c r="J62" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="K62" s="9">
-        <v>6.83E-2</v>
-      </c>
-      <c r="L62" s="10">
-        <v>311.3</v>
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="L62" s="8">
+        <v>308.7</v>
       </c>
       <c r="M62" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4445,37 +4453,37 @@
       <c r="N62" s="9">
         <v>0</v>
       </c>
-      <c r="O62" s="10">
+      <c r="O62" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="P62" s="9">
-        <v>6.83E-2</v>
-      </c>
-      <c r="Q62" s="10">
-        <v>311.3</v>
+        <v>7.6300000000000007E-2</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>308.7</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B63" s="7">
-        <v>220.5</v>
+        <v>201.5</v>
       </c>
       <c r="C63" s="7">
-        <v>200</v>
+        <v>218.5</v>
       </c>
       <c r="D63" s="7">
-        <v>225</v>
+        <v>226.5</v>
       </c>
       <c r="E63" s="7">
-        <v>191.5</v>
+        <v>196</v>
       </c>
       <c r="F63" s="8">
-        <v>-17</v>
+        <v>18.5</v>
       </c>
       <c r="G63" s="8">
-        <v>-7.83</v>
+        <v>9.25</v>
       </c>
       <c r="H63" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4483,14 +4491,14 @@
       <c r="I63" s="9">
         <v>0</v>
       </c>
-      <c r="J63" s="10">
+      <c r="J63" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="K63" s="9">
-        <v>6.0299999999999999E-2</v>
-      </c>
-      <c r="L63" s="10">
-        <v>315</v>
+        <v>6.83E-2</v>
+      </c>
+      <c r="L63" s="8">
+        <v>311.3</v>
       </c>
       <c r="M63" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4498,37 +4506,37 @@
       <c r="N63" s="9">
         <v>0</v>
       </c>
-      <c r="O63" s="10">
+      <c r="O63" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="P63" s="9">
-        <v>6.0299999999999999E-2</v>
-      </c>
-      <c r="Q63" s="10">
-        <v>315</v>
+        <v>6.83E-2</v>
+      </c>
+      <c r="Q63" s="8">
+        <v>311.3</v>
       </c>
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B64" s="7">
-        <v>222</v>
+        <v>220.5</v>
       </c>
       <c r="C64" s="7">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="D64" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E64" s="7">
-        <v>197</v>
-      </c>
-      <c r="F64" s="8">
-        <v>-4</v>
-      </c>
-      <c r="G64" s="8">
-        <v>-1.81</v>
+        <v>191.5</v>
+      </c>
+      <c r="F64" s="10">
+        <v>-17</v>
+      </c>
+      <c r="G64" s="10">
+        <v>-7.83</v>
       </c>
       <c r="H64" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4536,14 +4544,14 @@
       <c r="I64" s="9">
         <v>0</v>
       </c>
-      <c r="J64" s="10">
+      <c r="J64" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="K64" s="9">
-        <v>5.2299999999999999E-2</v>
-      </c>
-      <c r="L64" s="10">
-        <v>319.89999999999998</v>
+        <v>6.0299999999999999E-2</v>
+      </c>
+      <c r="L64" s="8">
+        <v>315</v>
       </c>
       <c r="M64" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4551,37 +4559,37 @@
       <c r="N64" s="9">
         <v>0</v>
       </c>
-      <c r="O64" s="10">
+      <c r="O64" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="P64" s="9">
-        <v>5.2299999999999999E-2</v>
-      </c>
-      <c r="Q64" s="10">
-        <v>319.89999999999998</v>
+        <v>6.0299999999999999E-2</v>
+      </c>
+      <c r="Q64" s="8">
+        <v>315</v>
       </c>
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B65" s="7">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="C65" s="7">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D65" s="7">
-        <v>229.5</v>
+        <v>224</v>
       </c>
       <c r="E65" s="7">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="F65" s="10">
-        <v>36.5</v>
+        <v>-4</v>
       </c>
       <c r="G65" s="10">
-        <v>19.78</v>
+        <v>-1.81</v>
       </c>
       <c r="H65" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4589,14 +4597,14 @@
       <c r="I65" s="9">
         <v>0</v>
       </c>
-      <c r="J65" s="10">
+      <c r="J65" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="K65" s="9">
-        <v>4.4299999999999999E-2</v>
-      </c>
-      <c r="L65" s="10">
-        <v>326.39999999999998</v>
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="L65" s="8">
+        <v>319.89999999999998</v>
       </c>
       <c r="M65" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4604,37 +4612,37 @@
       <c r="N65" s="9">
         <v>0</v>
       </c>
-      <c r="O65" s="10">
+      <c r="O65" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="P65" s="9">
-        <v>4.4299999999999999E-2</v>
-      </c>
-      <c r="Q65" s="10">
-        <v>326.39999999999998</v>
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="Q65" s="8">
+        <v>319.89999999999998</v>
       </c>
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B66" s="7">
-        <v>187.5</v>
+        <v>188</v>
       </c>
       <c r="C66" s="7">
-        <v>184.5</v>
+        <v>221</v>
       </c>
       <c r="D66" s="7">
-        <v>189.5</v>
+        <v>229.5</v>
       </c>
       <c r="E66" s="7">
-        <v>176.5</v>
+        <v>182</v>
       </c>
       <c r="F66" s="8">
-        <v>-5.5</v>
+        <v>36.5</v>
       </c>
       <c r="G66" s="8">
-        <v>-2.89</v>
+        <v>19.78</v>
       </c>
       <c r="H66" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4642,14 +4650,14 @@
       <c r="I66" s="9">
         <v>0</v>
       </c>
-      <c r="J66" s="10">
+      <c r="J66" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="K66" s="9">
-        <v>3.6200000000000003E-2</v>
-      </c>
-      <c r="L66" s="10">
-        <v>336.6</v>
+        <v>4.4299999999999999E-2</v>
+      </c>
+      <c r="L66" s="8">
+        <v>326.39999999999998</v>
       </c>
       <c r="M66" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4657,37 +4665,37 @@
       <c r="N66" s="9">
         <v>0</v>
       </c>
-      <c r="O66" s="10">
+      <c r="O66" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="P66" s="9">
-        <v>3.6200000000000003E-2</v>
-      </c>
-      <c r="Q66" s="10">
-        <v>336.6</v>
+        <v>4.4299999999999999E-2</v>
+      </c>
+      <c r="Q66" s="8">
+        <v>326.39999999999998</v>
       </c>
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B67" s="7">
-        <v>181</v>
+        <v>187.5</v>
       </c>
       <c r="C67" s="7">
-        <v>190</v>
+        <v>184.5</v>
       </c>
       <c r="D67" s="7">
-        <v>190</v>
+        <v>189.5</v>
       </c>
       <c r="E67" s="7">
-        <v>170</v>
+        <v>176.5</v>
       </c>
       <c r="F67" s="10">
-        <v>8.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G67" s="10">
-        <v>4.68</v>
+        <v>-2.89</v>
       </c>
       <c r="H67" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4695,14 +4703,14 @@
       <c r="I67" s="9">
         <v>0</v>
       </c>
-      <c r="J67" s="10">
+      <c r="J67" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="K67" s="9">
-        <v>2.8199999999999999E-2</v>
-      </c>
-      <c r="L67" s="10">
-        <v>352.8</v>
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="L67" s="8">
+        <v>336.6</v>
       </c>
       <c r="M67" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4710,37 +4718,37 @@
       <c r="N67" s="9">
         <v>0</v>
       </c>
-      <c r="O67" s="10">
+      <c r="O67" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="P67" s="9">
-        <v>2.8199999999999999E-2</v>
-      </c>
-      <c r="Q67" s="10">
-        <v>352.8</v>
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="Q67" s="8">
+        <v>336.6</v>
       </c>
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B68" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C68" s="7">
-        <v>181.5</v>
+        <v>190</v>
       </c>
       <c r="D68" s="7">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E68" s="7">
-        <v>166</v>
-      </c>
-      <c r="F68" s="10">
-        <v>3.5</v>
-      </c>
-      <c r="G68" s="10">
-        <v>1.97</v>
+        <v>170</v>
+      </c>
+      <c r="F68" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="G68" s="8">
+        <v>4.68</v>
       </c>
       <c r="H68" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4748,14 +4756,14 @@
       <c r="I68" s="9">
         <v>0</v>
       </c>
-      <c r="J68" s="10">
+      <c r="J68" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="K68" s="9">
-        <v>2.0199999999999999E-2</v>
-      </c>
-      <c r="L68" s="10">
-        <v>386.5</v>
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="L68" s="8">
+        <v>352.8</v>
       </c>
       <c r="M68" s="9">
         <v>8.0000000000000002E-3</v>
@@ -4763,143 +4771,143 @@
       <c r="N68" s="9">
         <v>0</v>
       </c>
-      <c r="O68" s="10">
+      <c r="O68" s="8">
         <v>285.60000000000002</v>
       </c>
       <c r="P68" s="9">
-        <v>2.0199999999999999E-2</v>
-      </c>
-      <c r="Q68" s="10">
-        <v>386.5</v>
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="Q68" s="8">
+        <v>352.8</v>
       </c>
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42795</v>
+        <v>42826</v>
       </c>
       <c r="B69" s="7">
-        <v>185.5</v>
+        <v>179</v>
       </c>
       <c r="C69" s="7">
-        <v>178</v>
+        <v>181.5</v>
       </c>
       <c r="D69" s="7">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="E69" s="7">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F69" s="8">
-        <v>-5.5</v>
+        <v>3.5</v>
       </c>
       <c r="G69" s="8">
-        <v>-3</v>
+        <v>1.97</v>
       </c>
       <c r="H69" s="9">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="I69" s="10">
+      <c r="I69" s="9">
+        <v>0</v>
+      </c>
+      <c r="J69" s="8">
         <v>285.60000000000002</v>
       </c>
-      <c r="J69" s="10">
-        <v>285.60000000000002</v>
-      </c>
       <c r="K69" s="9">
-        <v>1.2200000000000001E-2</v>
-      </c>
-      <c r="L69" s="10">
-        <v>485.1</v>
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="L69" s="8">
+        <v>386.5</v>
       </c>
       <c r="M69" s="9">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="N69" s="10">
+      <c r="N69" s="9">
+        <v>0</v>
+      </c>
+      <c r="O69" s="8">
         <v>285.60000000000002</v>
       </c>
-      <c r="O69" s="10">
-        <v>285.60000000000002</v>
-      </c>
       <c r="P69" s="9">
-        <v>1.2200000000000001E-2</v>
-      </c>
-      <c r="Q69" s="10">
-        <v>485.1</v>
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>386.5</v>
       </c>
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B70" s="7">
-        <v>161.5</v>
+        <v>185.5</v>
       </c>
       <c r="C70" s="7">
-        <v>183.5</v>
+        <v>178</v>
       </c>
       <c r="D70" s="7">
-        <v>195.5</v>
+        <v>208</v>
       </c>
       <c r="E70" s="7">
-        <v>157.5</v>
+        <v>175</v>
       </c>
       <c r="F70" s="10">
-        <v>23</v>
+        <v>-5.5</v>
       </c>
       <c r="G70" s="10">
-        <v>14.33</v>
+        <v>-3</v>
       </c>
       <c r="H70" s="9">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="I70" s="9">
-        <v>0</v>
-      </c>
-      <c r="J70" s="9" t="s">
-        <v>17</v>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I70" s="8">
+        <v>285.60000000000002</v>
+      </c>
+      <c r="J70" s="8">
+        <v>285.60000000000002</v>
       </c>
       <c r="K70" s="9">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="L70" s="9" t="s">
-        <v>17</v>
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="L70" s="8">
+        <v>485.1</v>
       </c>
       <c r="M70" s="9">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="N70" s="9">
-        <v>0</v>
-      </c>
-      <c r="O70" s="9" t="s">
-        <v>17</v>
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="N70" s="8">
+        <v>285.60000000000002</v>
+      </c>
+      <c r="O70" s="8">
+        <v>285.60000000000002</v>
       </c>
       <c r="P70" s="9">
-        <v>4.1999999999999997E-3</v>
-      </c>
-      <c r="Q70" s="9" t="s">
-        <v>17</v>
+        <v>1.2200000000000001E-2</v>
+      </c>
+      <c r="Q70" s="8">
+        <v>485.1</v>
       </c>
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B71" s="7">
-        <v>168.5</v>
+        <v>161.5</v>
       </c>
       <c r="C71" s="7">
-        <v>160.5</v>
+        <v>183.5</v>
       </c>
       <c r="D71" s="7">
-        <v>174.5</v>
+        <v>195.5</v>
       </c>
       <c r="E71" s="7">
-        <v>156.5</v>
+        <v>157.5</v>
       </c>
       <c r="F71" s="8">
-        <v>-6</v>
+        <v>23</v>
       </c>
       <c r="G71" s="8">
-        <v>-3.6</v>
+        <v>14.33</v>
       </c>
       <c r="H71" s="9">
         <v>2.0999999999999999E-3</v>
@@ -4911,7 +4919,7 @@
         <v>17</v>
       </c>
       <c r="K71" s="9">
-        <v>2.0999999999999999E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="L71" s="9" t="s">
         <v>17</v>
@@ -4926,7 +4934,7 @@
         <v>17</v>
       </c>
       <c r="P71" s="9">
-        <v>2.0999999999999999E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="Q71" s="9" t="s">
         <v>17</v>
@@ -4934,25 +4942,25 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B72" s="7">
-        <v>180</v>
+        <v>168.5</v>
       </c>
       <c r="C72" s="7">
-        <v>166.5</v>
+        <v>160.5</v>
       </c>
       <c r="D72" s="7">
-        <v>181</v>
+        <v>174.5</v>
       </c>
       <c r="E72" s="7">
-        <v>158</v>
-      </c>
-      <c r="F72" s="8">
-        <v>-12</v>
-      </c>
-      <c r="G72" s="8">
-        <v>-6.72</v>
+        <v>156.5</v>
+      </c>
+      <c r="F72" s="10">
+        <v>-6</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-3.6</v>
       </c>
       <c r="H72" s="9">
         <v>2.0999999999999999E-3</v>
@@ -4964,7 +4972,7 @@
         <v>17</v>
       </c>
       <c r="K72" s="9">
-        <v>2.0799999999999999E-2</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="L72" s="9" t="s">
         <v>17</v>
@@ -4979,7 +4987,7 @@
         <v>17</v>
       </c>
       <c r="P72" s="9">
-        <v>2.0799999999999999E-2</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="Q72" s="9" t="s">
         <v>17</v>
@@ -4987,25 +4995,25 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B73" s="7">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="C73" s="7">
-        <v>178.5</v>
+        <v>166.5</v>
       </c>
       <c r="D73" s="7">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="E73" s="7">
-        <v>174</v>
-      </c>
-      <c r="F73" s="8">
-        <v>-20</v>
-      </c>
-      <c r="G73" s="8">
-        <v>-10.08</v>
+        <v>158</v>
+      </c>
+      <c r="F73" s="10">
+        <v>-12</v>
+      </c>
+      <c r="G73" s="10">
+        <v>-6.72</v>
       </c>
       <c r="H73" s="9">
         <v>2.0999999999999999E-3</v>
@@ -5017,7 +5025,7 @@
         <v>17</v>
       </c>
       <c r="K73" s="9">
-        <v>1.8700000000000001E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="L73" s="9" t="s">
         <v>17</v>
@@ -5032,7 +5040,7 @@
         <v>17</v>
       </c>
       <c r="P73" s="9">
-        <v>1.8700000000000001E-2</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="Q73" s="9" t="s">
         <v>17</v>
@@ -5040,25 +5048,25 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B74" s="7">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="C74" s="7">
-        <v>198.5</v>
+        <v>178.5</v>
       </c>
       <c r="D74" s="7">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="E74" s="7">
-        <v>197</v>
-      </c>
-      <c r="F74" s="8">
-        <v>-19.5</v>
-      </c>
-      <c r="G74" s="8">
-        <v>-8.94</v>
+        <v>174</v>
+      </c>
+      <c r="F74" s="10">
+        <v>-20</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-10.08</v>
       </c>
       <c r="H74" s="9">
         <v>2.0999999999999999E-3</v>
@@ -5070,7 +5078,7 @@
         <v>17</v>
       </c>
       <c r="K74" s="9">
-        <v>1.66E-2</v>
+        <v>1.8700000000000001E-2</v>
       </c>
       <c r="L74" s="9" t="s">
         <v>17</v>
@@ -5085,7 +5093,7 @@
         <v>17</v>
       </c>
       <c r="P74" s="9">
-        <v>1.66E-2</v>
+        <v>1.8700000000000001E-2</v>
       </c>
       <c r="Q74" s="9" t="s">
         <v>17</v>
@@ -5093,25 +5101,25 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B75" s="7">
-        <v>196.5</v>
+        <v>219</v>
       </c>
       <c r="C75" s="7">
-        <v>218</v>
+        <v>198.5</v>
       </c>
       <c r="D75" s="7">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E75" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F75" s="10">
-        <v>21.5</v>
+        <v>-19.5</v>
       </c>
       <c r="G75" s="10">
-        <v>10.94</v>
+        <v>-8.94</v>
       </c>
       <c r="H75" s="9">
         <v>2.0999999999999999E-3</v>
@@ -5123,7 +5131,7 @@
         <v>17</v>
       </c>
       <c r="K75" s="9">
-        <v>1.4500000000000001E-2</v>
+        <v>1.66E-2</v>
       </c>
       <c r="L75" s="9" t="s">
         <v>17</v>
@@ -5138,7 +5146,7 @@
         <v>17</v>
       </c>
       <c r="P75" s="9">
-        <v>1.4500000000000001E-2</v>
+        <v>1.66E-2</v>
       </c>
       <c r="Q75" s="9" t="s">
         <v>17</v>
@@ -5146,25 +5154,25 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B76" s="7">
+        <v>196.5</v>
+      </c>
+      <c r="C76" s="7">
         <v>218</v>
       </c>
-      <c r="C76" s="7">
-        <v>196.5</v>
-      </c>
       <c r="D76" s="7">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E76" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F76" s="8">
-        <v>-20.5</v>
+        <v>21.5</v>
       </c>
       <c r="G76" s="8">
-        <v>-9.4499999999999993</v>
+        <v>10.94</v>
       </c>
       <c r="H76" s="9">
         <v>2.0999999999999999E-3</v>
@@ -5176,7 +5184,7 @@
         <v>17</v>
       </c>
       <c r="K76" s="9">
-        <v>1.24E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="L76" s="9" t="s">
         <v>17</v>
@@ -5191,7 +5199,7 @@
         <v>17</v>
       </c>
       <c r="P76" s="9">
-        <v>1.24E-2</v>
+        <v>1.4500000000000001E-2</v>
       </c>
       <c r="Q76" s="9" t="s">
         <v>17</v>
@@ -5199,25 +5207,25 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B77" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C77" s="7">
-        <v>217</v>
+        <v>196.5</v>
       </c>
       <c r="D77" s="7">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E77" s="7">
-        <v>208.5</v>
+        <v>193</v>
       </c>
       <c r="F77" s="10">
-        <v>1.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G77" s="10">
-        <v>0.7</v>
+        <v>-9.4499999999999993</v>
       </c>
       <c r="H77" s="9">
         <v>2.0999999999999999E-3</v>
@@ -5229,7 +5237,7 @@
         <v>17</v>
       </c>
       <c r="K77" s="9">
-        <v>1.04E-2</v>
+        <v>1.24E-2</v>
       </c>
       <c r="L77" s="9" t="s">
         <v>17</v>
@@ -5244,7 +5252,7 @@
         <v>17</v>
       </c>
       <c r="P77" s="9">
-        <v>1.04E-2</v>
+        <v>1.24E-2</v>
       </c>
       <c r="Q77" s="9" t="s">
         <v>17</v>
@@ -5252,25 +5260,25 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B78" s="7">
-        <v>260.5</v>
+        <v>217</v>
       </c>
       <c r="C78" s="7">
-        <v>215.5</v>
+        <v>217</v>
       </c>
       <c r="D78" s="7">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="E78" s="7">
-        <v>208</v>
+        <v>208.5</v>
       </c>
       <c r="F78" s="8">
-        <v>-44</v>
+        <v>1.5</v>
       </c>
       <c r="G78" s="8">
-        <v>-16.96</v>
+        <v>0.7</v>
       </c>
       <c r="H78" s="9">
         <v>2.0999999999999999E-3</v>
@@ -5282,7 +5290,7 @@
         <v>17</v>
       </c>
       <c r="K78" s="9">
-        <v>8.3000000000000001E-3</v>
+        <v>1.04E-2</v>
       </c>
       <c r="L78" s="9" t="s">
         <v>17</v>
@@ -5297,7 +5305,7 @@
         <v>17</v>
       </c>
       <c r="P78" s="9">
-        <v>8.3000000000000001E-3</v>
+        <v>1.04E-2</v>
       </c>
       <c r="Q78" s="9" t="s">
         <v>17</v>
@@ -5305,25 +5313,25 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B79" s="7">
-        <v>194.5</v>
+        <v>260.5</v>
       </c>
       <c r="C79" s="7">
-        <v>259.5</v>
+        <v>215.5</v>
       </c>
       <c r="D79" s="7">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="E79" s="7">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="F79" s="10">
-        <v>65</v>
+        <v>-44</v>
       </c>
       <c r="G79" s="10">
-        <v>33.42</v>
+        <v>-16.96</v>
       </c>
       <c r="H79" s="9">
         <v>2.0999999999999999E-3</v>
@@ -5335,7 +5343,7 @@
         <v>17</v>
       </c>
       <c r="K79" s="9">
-        <v>6.1999999999999998E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="L79" s="9" t="s">
         <v>17</v>
@@ -5350,7 +5358,7 @@
         <v>17</v>
       </c>
       <c r="P79" s="9">
-        <v>6.1999999999999998E-3</v>
+        <v>8.3000000000000001E-3</v>
       </c>
       <c r="Q79" s="9" t="s">
         <v>17</v>
@@ -5358,25 +5366,25 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B80" s="7">
-        <v>212</v>
+        <v>194.5</v>
       </c>
       <c r="C80" s="7">
-        <v>194.5</v>
+        <v>259.5</v>
       </c>
       <c r="D80" s="7">
-        <v>216.5</v>
+        <v>269</v>
       </c>
       <c r="E80" s="7">
-        <v>165.5</v>
+        <v>191</v>
       </c>
       <c r="F80" s="8">
-        <v>-22.5</v>
+        <v>65</v>
       </c>
       <c r="G80" s="8">
-        <v>-10.37</v>
+        <v>33.42</v>
       </c>
       <c r="H80" s="9">
         <v>2.0999999999999999E-3</v>
@@ -5388,7 +5396,7 @@
         <v>17</v>
       </c>
       <c r="K80" s="9">
-        <v>4.1999999999999997E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="L80" s="9" t="s">
         <v>17</v>
@@ -5403,7 +5411,7 @@
         <v>17</v>
       </c>
       <c r="P80" s="9">
-        <v>4.1999999999999997E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="Q80" s="9" t="s">
         <v>17</v>
@@ -5411,37 +5419,37 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B81" s="7">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C81" s="7">
-        <v>217</v>
+        <v>194.5</v>
       </c>
       <c r="D81" s="7">
-        <v>230.5</v>
+        <v>216.5</v>
       </c>
       <c r="E81" s="7">
-        <v>186.5</v>
+        <v>165.5</v>
       </c>
       <c r="F81" s="10">
-        <v>16.5</v>
+        <v>-22.5</v>
       </c>
       <c r="G81" s="10">
-        <v>8.23</v>
+        <v>-10.37</v>
       </c>
       <c r="H81" s="9">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="I81" s="9" t="s">
-        <v>17</v>
+      <c r="I81" s="9">
+        <v>0</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K81" s="9">
-        <v>2.0999999999999999E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="L81" s="9" t="s">
         <v>17</v>
@@ -5449,14 +5457,14 @@
       <c r="M81" s="9">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="N81" s="9" t="s">
-        <v>17</v>
+      <c r="N81" s="9">
+        <v>0</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P81" s="9">
-        <v>2.0999999999999999E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="Q81" s="9" t="s">
         <v>17</v>
@@ -5464,28 +5472,28 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B82" s="7">
-        <v>238</v>
+        <v>201</v>
       </c>
       <c r="C82" s="7">
-        <v>200.5</v>
+        <v>217</v>
       </c>
       <c r="D82" s="7">
-        <v>240</v>
+        <v>230.5</v>
       </c>
       <c r="E82" s="7">
-        <v>183.5</v>
+        <v>186.5</v>
       </c>
       <c r="F82" s="8">
-        <v>-36.5</v>
+        <v>16.5</v>
       </c>
       <c r="G82" s="8">
-        <v>-15.4</v>
+        <v>8.23</v>
       </c>
       <c r="H82" s="9">
-        <v>0</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="I82" s="9" t="s">
         <v>17</v>
@@ -5494,13 +5502,13 @@
         <v>17</v>
       </c>
       <c r="K82" s="9">
-        <v>0</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="L82" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M82" s="9">
-        <v>0</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="N82" s="9" t="s">
         <v>17</v>
@@ -5509,7 +5517,7 @@
         <v>17</v>
       </c>
       <c r="P82" s="9">
-        <v>0</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="Q82" s="9" t="s">
         <v>17</v>
@@ -5517,25 +5525,25 @@
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B83" s="7">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="C83" s="7">
-        <v>237</v>
+        <v>200.5</v>
       </c>
       <c r="D83" s="7">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E83" s="7">
-        <v>201</v>
-      </c>
-      <c r="F83" s="8">
-        <v>-20.5</v>
-      </c>
-      <c r="G83" s="8">
-        <v>-7.96</v>
+        <v>183.5</v>
+      </c>
+      <c r="F83" s="10">
+        <v>-36.5</v>
+      </c>
+      <c r="G83" s="10">
+        <v>-15.4</v>
       </c>
       <c r="H83" s="9">
         <v>0</v>
@@ -5570,25 +5578,25 @@
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B84" s="7">
-        <v>214.5</v>
+        <v>249</v>
       </c>
       <c r="C84" s="7">
-        <v>257.5</v>
+        <v>237</v>
       </c>
       <c r="D84" s="7">
-        <v>303</v>
+        <v>257</v>
       </c>
       <c r="E84" s="7">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F84" s="10">
-        <v>43.5</v>
+        <v>-20.5</v>
       </c>
       <c r="G84" s="10">
-        <v>20.329999999999998</v>
+        <v>-7.96</v>
       </c>
       <c r="H84" s="9">
         <v>0</v>
@@ -5623,25 +5631,25 @@
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B85" s="7">
-        <v>146</v>
+        <v>214.5</v>
       </c>
       <c r="C85" s="7">
-        <v>214</v>
+        <v>257.5</v>
       </c>
       <c r="D85" s="7">
-        <v>219</v>
+        <v>303</v>
       </c>
       <c r="E85" s="7">
-        <v>146</v>
-      </c>
-      <c r="F85" s="10">
-        <v>99</v>
-      </c>
-      <c r="G85" s="10">
-        <v>86.09</v>
+        <v>210</v>
+      </c>
+      <c r="F85" s="8">
+        <v>43.5</v>
+      </c>
+      <c r="G85" s="8">
+        <v>20.329999999999998</v>
       </c>
       <c r="H85" s="9">
         <v>0</v>
@@ -5676,25 +5684,25 @@
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42278</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>17</v>
+        <v>42309</v>
+      </c>
+      <c r="B86" s="7">
+        <v>146</v>
+      </c>
+      <c r="C86" s="7">
+        <v>214</v>
+      </c>
+      <c r="D86" s="7">
+        <v>219</v>
+      </c>
+      <c r="E86" s="7">
+        <v>146</v>
+      </c>
+      <c r="F86" s="8">
+        <v>99</v>
+      </c>
+      <c r="G86" s="8">
+        <v>86.09</v>
       </c>
       <c r="H86" s="9">
         <v>0</v>
@@ -5729,7 +5737,7 @@
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>17</v>
@@ -5782,7 +5790,7 @@
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>17</v>
@@ -5835,7 +5843,7 @@
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>42186</v>
+        <v>42217</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>17</v>
@@ -5888,7 +5896,7 @@
     </row>
     <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>42156</v>
+        <v>42186</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>17</v>
@@ -5941,7 +5949,7 @@
     </row>
     <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>42125</v>
+        <v>42156</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>17</v>
@@ -5994,7 +6002,7 @@
     </row>
     <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>42095</v>
+        <v>42125</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>17</v>
@@ -6047,7 +6055,7 @@
     </row>
     <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>42064</v>
+        <v>42095</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>17</v>
@@ -6100,7 +6108,7 @@
     </row>
     <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>42036</v>
+        <v>42064</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>17</v>
@@ -6153,7 +6161,7 @@
     </row>
     <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>42005</v>
+        <v>42036</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>17</v>
@@ -6206,7 +6214,7 @@
     </row>
     <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>41974</v>
+        <v>42005</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>17</v>
@@ -6259,7 +6267,7 @@
     </row>
     <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
-        <v>41944</v>
+        <v>41974</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>17</v>
@@ -6312,7 +6320,7 @@
     </row>
     <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
-        <v>41913</v>
+        <v>41944</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>17</v>
@@ -6365,7 +6373,7 @@
     </row>
     <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
-        <v>41883</v>
+        <v>41913</v>
       </c>
       <c r="B99" s="7" t="s">
         <v>17</v>
@@ -6418,7 +6426,7 @@
     </row>
     <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
-        <v>41852</v>
+        <v>41883</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>17</v>
@@ -6471,7 +6479,7 @@
     </row>
     <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
-        <v>41821</v>
+        <v>41852</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>17</v>
@@ -6524,7 +6532,7 @@
     </row>
     <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
-        <v>41791</v>
+        <v>41821</v>
       </c>
       <c r="B102" s="7" t="s">
         <v>17</v>
@@ -6577,7 +6585,7 @@
     </row>
     <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
-        <v>41760</v>
+        <v>41791</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>17</v>
@@ -6630,7 +6638,7 @@
     </row>
     <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
-        <v>41730</v>
+        <v>41760</v>
       </c>
       <c r="B104" s="7" t="s">
         <v>17</v>
@@ -6683,7 +6691,7 @@
     </row>
     <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
-        <v>41699</v>
+        <v>41730</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>17</v>
@@ -6736,7 +6744,7 @@
     </row>
     <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
-        <v>41671</v>
+        <v>41699</v>
       </c>
       <c r="B106" s="7" t="s">
         <v>17</v>
@@ -6789,7 +6797,7 @@
     </row>
     <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
-        <v>41640</v>
+        <v>41671</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>17</v>
@@ -6842,7 +6850,7 @@
     </row>
     <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
-        <v>41609</v>
+        <v>41640</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>17</v>
@@ -6895,7 +6903,7 @@
     </row>
     <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
-        <v>41579</v>
+        <v>41609</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>17</v>
@@ -6948,7 +6956,7 @@
     </row>
     <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
-        <v>41548</v>
+        <v>41579</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>17</v>
@@ -7001,7 +7009,7 @@
     </row>
     <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
-        <v>41518</v>
+        <v>41548</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>17</v>
@@ -7054,7 +7062,7 @@
     </row>
     <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
-        <v>41487</v>
+        <v>41518</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>17</v>
@@ -7107,7 +7115,7 @@
     </row>
     <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
-        <v>41456</v>
+        <v>41487</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>17</v>
@@ -7160,7 +7168,7 @@
     </row>
     <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
-        <v>41426</v>
+        <v>41456</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>17</v>
@@ -7213,7 +7221,7 @@
     </row>
     <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
-        <v>41395</v>
+        <v>41426</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>17</v>
@@ -7266,7 +7274,7 @@
     </row>
     <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
-        <v>41365</v>
+        <v>41395</v>
       </c>
       <c r="B116" s="7" t="s">
         <v>17</v>
@@ -7319,7 +7327,7 @@
     </row>
     <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
-        <v>41334</v>
+        <v>41365</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>17</v>
@@ -7372,7 +7380,7 @@
     </row>
     <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
-        <v>41306</v>
+        <v>41334</v>
       </c>
       <c r="B118" s="7" t="s">
         <v>17</v>
@@ -7425,7 +7433,7 @@
     </row>
     <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
-        <v>41275</v>
+        <v>41306</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>17</v>
@@ -7478,7 +7486,7 @@
     </row>
     <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
-        <v>41244</v>
+        <v>41275</v>
       </c>
       <c r="B120" s="7" t="s">
         <v>17</v>
@@ -7510,11 +7518,11 @@
       <c r="K120" s="9">
         <v>0</v>
       </c>
-      <c r="L120" s="8">
-        <v>-100</v>
-      </c>
-      <c r="M120" s="9" t="s">
-        <v>17</v>
+      <c r="L120" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M120" s="9">
+        <v>0</v>
       </c>
       <c r="N120" s="9" t="s">
         <v>17</v>
@@ -7522,8 +7530,8 @@
       <c r="O120" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="P120" s="9" t="s">
-        <v>17</v>
+      <c r="P120" s="9">
+        <v>0</v>
       </c>
       <c r="Q120" s="9" t="s">
         <v>17</v>
@@ -7531,7 +7539,7 @@
     </row>
     <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
-        <v>41214</v>
+        <v>41244</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>17</v>
@@ -7563,7 +7571,7 @@
       <c r="K121" s="9">
         <v>0</v>
       </c>
-      <c r="L121" s="8">
+      <c r="L121" s="10">
         <v>-100</v>
       </c>
       <c r="M121" s="9" t="s">
@@ -7584,7 +7592,7 @@
     </row>
     <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
-        <v>41183</v>
+        <v>41214</v>
       </c>
       <c r="B122" s="7" t="s">
         <v>17</v>
@@ -7616,7 +7624,7 @@
       <c r="K122" s="9">
         <v>0</v>
       </c>
-      <c r="L122" s="8">
+      <c r="L122" s="10">
         <v>-100</v>
       </c>
       <c r="M122" s="9" t="s">
@@ -7637,7 +7645,7 @@
     </row>
     <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
-        <v>41153</v>
+        <v>41183</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>17</v>
@@ -7669,7 +7677,7 @@
       <c r="K123" s="9">
         <v>0</v>
       </c>
-      <c r="L123" s="8">
+      <c r="L123" s="10">
         <v>-100</v>
       </c>
       <c r="M123" s="9" t="s">
@@ -7690,7 +7698,7 @@
     </row>
     <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
-        <v>41122</v>
+        <v>41153</v>
       </c>
       <c r="B124" s="7" t="s">
         <v>17</v>
@@ -7722,7 +7730,7 @@
       <c r="K124" s="9">
         <v>0</v>
       </c>
-      <c r="L124" s="8">
+      <c r="L124" s="10">
         <v>-100</v>
       </c>
       <c r="M124" s="9" t="s">
@@ -7743,7 +7751,7 @@
     </row>
     <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
-        <v>41091</v>
+        <v>41122</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>17</v>
@@ -7775,7 +7783,7 @@
       <c r="K125" s="9">
         <v>0</v>
       </c>
-      <c r="L125" s="8">
+      <c r="L125" s="10">
         <v>-100</v>
       </c>
       <c r="M125" s="9" t="s">
@@ -7796,7 +7804,7 @@
     </row>
     <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
-        <v>41061</v>
+        <v>41091</v>
       </c>
       <c r="B126" s="7" t="s">
         <v>17</v>
@@ -7828,7 +7836,7 @@
       <c r="K126" s="9">
         <v>0</v>
       </c>
-      <c r="L126" s="8">
+      <c r="L126" s="10">
         <v>-100</v>
       </c>
       <c r="M126" s="9" t="s">
@@ -7849,7 +7857,7 @@
     </row>
     <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
-        <v>41030</v>
+        <v>41061</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>17</v>
@@ -7881,7 +7889,7 @@
       <c r="K127" s="9">
         <v>0</v>
       </c>
-      <c r="L127" s="8">
+      <c r="L127" s="10">
         <v>-100</v>
       </c>
       <c r="M127" s="9" t="s">
@@ -7902,7 +7910,7 @@
     </row>
     <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
-        <v>41000</v>
+        <v>41030</v>
       </c>
       <c r="B128" s="7" t="s">
         <v>17</v>
@@ -7934,7 +7942,7 @@
       <c r="K128" s="9">
         <v>0</v>
       </c>
-      <c r="L128" s="8">
+      <c r="L128" s="10">
         <v>-100</v>
       </c>
       <c r="M128" s="9" t="s">
@@ -7955,7 +7963,7 @@
     </row>
     <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
-        <v>40969</v>
+        <v>41000</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>17</v>
@@ -7981,13 +7989,13 @@
       <c r="I129" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J129" s="8">
-        <v>-100</v>
+      <c r="J129" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K129" s="9">
         <v>0</v>
       </c>
-      <c r="L129" s="8">
+      <c r="L129" s="10">
         <v>-100</v>
       </c>
       <c r="M129" s="9" t="s">
@@ -8008,7 +8016,7 @@
     </row>
     <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
-        <v>40940</v>
+        <v>40969</v>
       </c>
       <c r="B130" s="7" t="s">
         <v>17</v>
@@ -8034,13 +8042,13 @@
       <c r="I130" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J130" s="8">
+      <c r="J130" s="10">
         <v>-100</v>
       </c>
       <c r="K130" s="9">
         <v>0</v>
       </c>
-      <c r="L130" s="8">
+      <c r="L130" s="10">
         <v>-100</v>
       </c>
       <c r="M130" s="9" t="s">
@@ -8061,7 +8069,7 @@
     </row>
     <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
-        <v>40909</v>
+        <v>40940</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>17</v>
@@ -8087,13 +8095,13 @@
       <c r="I131" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J131" s="8">
+      <c r="J131" s="10">
         <v>-100</v>
       </c>
       <c r="K131" s="9">
         <v>0</v>
       </c>
-      <c r="L131" s="8">
+      <c r="L131" s="10">
         <v>-100</v>
       </c>
       <c r="M131" s="9" t="s">
@@ -8114,7 +8122,7 @@
     </row>
     <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
-        <v>40878</v>
+        <v>40909</v>
       </c>
       <c r="B132" s="7" t="s">
         <v>17</v>
@@ -8140,14 +8148,14 @@
       <c r="I132" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J132" s="8">
+      <c r="J132" s="10">
         <v>-100</v>
       </c>
       <c r="K132" s="9">
-        <v>1.4E-3</v>
-      </c>
-      <c r="L132" s="8">
-        <v>-57.7</v>
+        <v>0</v>
+      </c>
+      <c r="L132" s="10">
+        <v>-100</v>
       </c>
       <c r="M132" s="9" t="s">
         <v>17</v>
@@ -8167,7 +8175,7 @@
     </row>
     <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
-        <v>40848</v>
+        <v>40878</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>17</v>
@@ -8193,14 +8201,14 @@
       <c r="I133" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J133" s="8">
+      <c r="J133" s="10">
         <v>-100</v>
       </c>
       <c r="K133" s="9">
         <v>1.4E-3</v>
       </c>
       <c r="L133" s="10">
-        <v>50</v>
+        <v>-57.7</v>
       </c>
       <c r="M133" s="9" t="s">
         <v>17</v>
@@ -8220,7 +8228,7 @@
     </row>
     <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
-        <v>40817</v>
+        <v>40848</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>17</v>
@@ -8246,14 +8254,14 @@
       <c r="I134" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J134" s="8">
+      <c r="J134" s="10">
         <v>-100</v>
       </c>
       <c r="K134" s="9">
         <v>1.4E-3</v>
       </c>
-      <c r="L134" s="10">
-        <v>200</v>
+      <c r="L134" s="8">
+        <v>50</v>
       </c>
       <c r="M134" s="9" t="s">
         <v>17</v>
@@ -8273,7 +8281,7 @@
     </row>
     <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
-        <v>40787</v>
+        <v>40817</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>17</v>
@@ -8299,14 +8307,14 @@
       <c r="I135" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J135" s="9" t="s">
-        <v>17</v>
+      <c r="J135" s="10">
+        <v>-100</v>
       </c>
       <c r="K135" s="9">
         <v>1.4E-3</v>
       </c>
-      <c r="L135" s="9" t="s">
-        <v>17</v>
+      <c r="L135" s="8">
+        <v>200</v>
       </c>
       <c r="M135" s="9" t="s">
         <v>17</v>
@@ -8326,7 +8334,7 @@
     </row>
     <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
-        <v>40756</v>
+        <v>40787</v>
       </c>
       <c r="B136" s="7" t="s">
         <v>17</v>
@@ -8379,7 +8387,7 @@
     </row>
     <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
-        <v>40725</v>
+        <v>40756</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>17</v>
@@ -8432,7 +8440,7 @@
     </row>
     <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
-        <v>40695</v>
+        <v>40725</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>17</v>
@@ -8485,7 +8493,7 @@
     </row>
     <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
-        <v>40664</v>
+        <v>40695</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>17</v>
@@ -8538,7 +8546,7 @@
     </row>
     <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
-        <v>40634</v>
+        <v>40664</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>17</v>
@@ -8561,8 +8569,8 @@
       <c r="H140" s="9">
         <v>0</v>
       </c>
-      <c r="I140" s="8">
-        <v>-100</v>
+      <c r="I140" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J140" s="9" t="s">
         <v>17</v>
@@ -8591,7 +8599,7 @@
     </row>
     <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
-        <v>40603</v>
+        <v>40634</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>17</v>
@@ -8612,10 +8620,10 @@
         <v>17</v>
       </c>
       <c r="H141" s="9">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="I141" s="9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I141" s="10">
+        <v>-100</v>
       </c>
       <c r="J141" s="9" t="s">
         <v>17</v>
@@ -8644,7 +8652,7 @@
     </row>
     <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
-        <v>40575</v>
+        <v>40603</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>17</v>
@@ -8674,7 +8682,7 @@
         <v>17</v>
       </c>
       <c r="K142" s="9">
-        <v>8.9999999999999998E-4</v>
+        <v>1.4E-3</v>
       </c>
       <c r="L142" s="9" t="s">
         <v>17</v>
@@ -8697,7 +8705,7 @@
     </row>
     <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
-        <v>40544</v>
+        <v>40575</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>17</v>
@@ -8720,14 +8728,14 @@
       <c r="H143" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I143" s="8">
-        <v>-80.3</v>
+      <c r="I143" s="9">
+        <v>0</v>
       </c>
       <c r="J143" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K143" s="9">
-        <v>4.0000000000000002E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="L143" s="9" t="s">
         <v>17</v>
@@ -8750,7 +8758,7 @@
     </row>
     <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
-        <v>40513</v>
+        <v>40544</v>
       </c>
       <c r="B144" s="7" t="s">
         <v>17</v>
@@ -8771,16 +8779,16 @@
         <v>17</v>
       </c>
       <c r="H144" s="9">
-        <v>2.3E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="I144" s="10">
-        <v>408.9</v>
+        <v>-80.3</v>
       </c>
       <c r="J144" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K144" s="9">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="L144" s="9" t="s">
         <v>17</v>
@@ -8803,7 +8811,7 @@
     </row>
     <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
-        <v>40483</v>
+        <v>40513</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>17</v>
@@ -8824,16 +8832,16 @@
         <v>17</v>
       </c>
       <c r="H145" s="9">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="I145" s="9">
-        <v>0</v>
+        <v>2.3E-3</v>
+      </c>
+      <c r="I145" s="8">
+        <v>408.9</v>
       </c>
       <c r="J145" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K145" s="9">
-        <v>8.9999999999999998E-4</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="L145" s="9" t="s">
         <v>17</v>
@@ -8856,7 +8864,7 @@
     </row>
     <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
-        <v>40452</v>
+        <v>40483</v>
       </c>
       <c r="B146" s="7" t="s">
         <v>17</v>
@@ -8879,14 +8887,14 @@
       <c r="H146" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="I146" s="9" t="s">
-        <v>17</v>
+      <c r="I146" s="9">
+        <v>0</v>
       </c>
       <c r="J146" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K146" s="9">
-        <v>4.0000000000000002E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="L146" s="9" t="s">
         <v>17</v>
@@ -8909,7 +8917,7 @@
     </row>
     <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>40422</v>
+        <v>40452</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>17</v>
@@ -8930,7 +8938,7 @@
         <v>17</v>
       </c>
       <c r="H147" s="9">
-        <v>0</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="I147" s="9" t="s">
         <v>17</v>
@@ -8939,7 +8947,7 @@
         <v>17</v>
       </c>
       <c r="K147" s="9">
-        <v>0</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="L147" s="9" t="s">
         <v>17</v>
@@ -8962,7 +8970,7 @@
     </row>
     <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
-        <v>40391</v>
+        <v>40422</v>
       </c>
       <c r="B148" s="7" t="s">
         <v>17</v>
@@ -9015,7 +9023,7 @@
     </row>
     <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
-        <v>40360</v>
+        <v>40391</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>17</v>
@@ -9068,7 +9076,7 @@
     </row>
     <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
-        <v>40330</v>
+        <v>40360</v>
       </c>
       <c r="B150" s="7" t="s">
         <v>17</v>
@@ -9121,54 +9129,107 @@
     </row>
     <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
+        <v>40330</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H151" s="9">
+        <v>0</v>
+      </c>
+      <c r="I151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K151" s="9">
+        <v>0</v>
+      </c>
+      <c r="L151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q151" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
         <v>40299</v>
       </c>
-      <c r="B151" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D151" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E151" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F151" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G151" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H151" s="9">
-        <v>0</v>
-      </c>
-      <c r="I151" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J151" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K151" s="9">
-        <v>0</v>
-      </c>
-      <c r="L151" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M151" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N151" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O151" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="P151" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q151" s="9" t="s">
+      <c r="B152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H152" s="9">
+        <v>0</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K152" s="9">
+        <v>0</v>
+      </c>
+      <c r="L152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q152" s="9" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9187,7 +9248,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>